--- a/Tabla_Resultados_Corrida.xlsx
+++ b/Tabla_Resultados_Corrida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Models\mi-proyecto-anylogic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E379214-C952-4EB7-8EBE-99D54ABCA051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFB0AF7-A730-4F0B-A59D-03C43D4D0F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A923D075-8E6E-4AD4-8B2A-316AD42E9CB3}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="48">
   <si>
     <t>Dia</t>
   </si>
@@ -58,43 +58,7 @@
     <t>Hora</t>
   </si>
   <si>
-    <t>EntExt</t>
-  </si>
-  <si>
-    <t>SalExt</t>
-  </si>
-  <si>
-    <t>OcupExt</t>
-  </si>
-  <si>
-    <t>EntCent</t>
-  </si>
-  <si>
-    <t>SalCent</t>
-  </si>
-  <si>
-    <t>OcupCent</t>
-  </si>
-  <si>
-    <t>EntPoli</t>
-  </si>
-  <si>
-    <t>SalPoli</t>
-  </si>
-  <si>
-    <t>OcupPoli</t>
-  </si>
-  <si>
-    <t>EntTotal</t>
-  </si>
-  <si>
-    <t>SalTotal</t>
-  </si>
-  <si>
     <t>OcupTotal</t>
-  </si>
-  <si>
-    <t>Rechazados</t>
   </si>
   <si>
     <t>Lunes 9</t>
@@ -180,6 +144,57 @@
   <si>
     <t>Viernes 13</t>
   </si>
+  <si>
+    <t>Entradas Externo</t>
+  </si>
+  <si>
+    <t>Salidas Externo</t>
+  </si>
+  <si>
+    <t>Ocupación Externo</t>
+  </si>
+  <si>
+    <t>Rechazados acumulados</t>
+  </si>
+  <si>
+    <t>Entradas Central</t>
+  </si>
+  <si>
+    <t>Salidas Central</t>
+  </si>
+  <si>
+    <t>Ocupación Central</t>
+  </si>
+  <si>
+    <t>Entradas Polideportivo</t>
+  </si>
+  <si>
+    <t>Salidas Polideportivo</t>
+  </si>
+  <si>
+    <t>Ocupación Polideportivo</t>
+  </si>
+  <si>
+    <t>Entradas Total</t>
+  </si>
+  <si>
+    <t>Salidas Total</t>
+  </si>
+  <si>
+    <t>% Utilización Total</t>
+  </si>
+  <si>
+    <t>% Utilización Externo</t>
+  </si>
+  <si>
+    <t>% Utilización Central</t>
+  </si>
+  <si>
+    <t>% Utilización Polideportivo</t>
+  </si>
+  <si>
+    <t>Rechazados por hora</t>
+  </si>
 </sst>
 </file>
 
@@ -222,15 +237,1023 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="106">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -252,8 +1275,8 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatosExternos_1" connectionId="1" xr16:uid="{2AC9290E-AD61-461B-A21A-34496DBF1F3A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="16">
-    <queryTableFields count="15">
+  <queryTableRefresh nextId="22" unboundColumnsRight="5">
+    <queryTableFields count="20">
       <queryTableField id="1" name="Dia" tableColumnId="1"/>
       <queryTableField id="2" name="Hora" tableColumnId="2"/>
       <queryTableField id="3" name="EntExt" tableColumnId="3"/>
@@ -269,30 +1292,70 @@
       <queryTableField id="13" name="SalTotal" tableColumnId="13"/>
       <queryTableField id="14" name="OcupTotal" tableColumnId="14"/>
       <queryTableField id="15" name="Rechazados" tableColumnId="15"/>
+      <queryTableField id="17" dataBound="0" tableColumnId="17"/>
+      <queryTableField id="18" dataBound="0" tableColumnId="18"/>
+      <queryTableField id="19" dataBound="0" tableColumnId="19"/>
+      <queryTableField id="20" dataBound="0" tableColumnId="20"/>
+      <queryTableField id="21" dataBound="0" tableColumnId="21"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74F22340-4DCC-48B2-97CE-82C3B5869135}" name="output" displayName="output" ref="A1:O104" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O104" xr:uid="{74F22340-4DCC-48B2-97CE-82C3B5869135}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{29BADEF3-00F3-4923-9B25-9276A2AB6AF3}" uniqueName="1" name="Dia" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{7FF5DB85-B9DE-4A5F-8C22-4E66327D084E}" uniqueName="2" name="Hora" queryTableFieldId="2" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{06DDC69D-1405-41D2-A484-702BD6EB6B49}" uniqueName="3" name="EntExt" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{EF2FE910-1170-47C3-9301-CB1EDF69007F}" uniqueName="4" name="SalExt" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{CDF657CF-72AD-48AD-A9F4-18C306027810}" uniqueName="5" name="OcupExt" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{366FE8A2-1B85-488D-A618-DC32FCF3A8A4}" uniqueName="6" name="EntCent" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{0593EFA6-903D-4A35-80F7-F3EC8A432016}" uniqueName="7" name="SalCent" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{933EAB70-E024-45CE-AFAF-5065F92541C8}" uniqueName="8" name="OcupCent" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{E354DEF6-8248-4473-A467-38B0F1AE3D94}" uniqueName="9" name="EntPoli" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{8B115D59-DA50-46C7-9547-C01760D8BED9}" uniqueName="10" name="SalPoli" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{51016732-5ADF-4005-BDE7-121E93E15233}" uniqueName="11" name="OcupPoli" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{F0879C00-59C2-419C-8538-41F17FA72E12}" uniqueName="12" name="EntTotal" queryTableFieldId="12"/>
-    <tableColumn id="13" xr3:uid="{CA0D0D81-2959-4048-B568-C2A3ECAE3564}" uniqueName="13" name="SalTotal" queryTableFieldId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74F22340-4DCC-48B2-97CE-82C3B5869135}" name="output" displayName="output" ref="A1:T104" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:T104" xr:uid="{74F22340-4DCC-48B2-97CE-82C3B5869135}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="07:00 - 08:00"/>
+        <filter val="08:00 - 09:00"/>
+        <filter val="09:00 - 10:00"/>
+        <filter val="10:00 - 11:00"/>
+        <filter val="11:00 - 12:00"/>
+        <filter val="12:00 - 13:00"/>
+        <filter val="13:00 - 14:00"/>
+        <filter val="14:00 - 15:00"/>
+        <filter val="15:00 - 16:00"/>
+        <filter val="16:00 - 17:00"/>
+        <filter val="17:00 - 18:00"/>
+        <filter val="18:00 - 19:00"/>
+        <filter val="19:00 - 20:00"/>
+        <filter val="20:00 - 21:00"/>
+        <filter val="21:00 - 22:00"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{29BADEF3-00F3-4923-9B25-9276A2AB6AF3}" uniqueName="1" name="Dia" queryTableFieldId="1" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{7FF5DB85-B9DE-4A5F-8C22-4E66327D084E}" uniqueName="2" name="Hora" queryTableFieldId="2" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{06DDC69D-1405-41D2-A484-702BD6EB6B49}" uniqueName="3" name="Entradas Externo" queryTableFieldId="3"/>
+    <tableColumn id="4" xr3:uid="{EF2FE910-1170-47C3-9301-CB1EDF69007F}" uniqueName="4" name="Salidas Externo" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{CDF657CF-72AD-48AD-A9F4-18C306027810}" uniqueName="5" name="Ocupación Externo" queryTableFieldId="5"/>
+    <tableColumn id="6" xr3:uid="{366FE8A2-1B85-488D-A618-DC32FCF3A8A4}" uniqueName="6" name="Entradas Central" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{0593EFA6-903D-4A35-80F7-F3EC8A432016}" uniqueName="7" name="Salidas Central" queryTableFieldId="7"/>
+    <tableColumn id="8" xr3:uid="{933EAB70-E024-45CE-AFAF-5065F92541C8}" uniqueName="8" name="Ocupación Central" queryTableFieldId="8"/>
+    <tableColumn id="9" xr3:uid="{E354DEF6-8248-4473-A467-38B0F1AE3D94}" uniqueName="9" name="Entradas Polideportivo" queryTableFieldId="9"/>
+    <tableColumn id="10" xr3:uid="{8B115D59-DA50-46C7-9547-C01760D8BED9}" uniqueName="10" name="Salidas Polideportivo" queryTableFieldId="10"/>
+    <tableColumn id="11" xr3:uid="{51016732-5ADF-4005-BDE7-121E93E15233}" uniqueName="11" name="Ocupación Polideportivo" queryTableFieldId="11"/>
+    <tableColumn id="12" xr3:uid="{F0879C00-59C2-419C-8538-41F17FA72E12}" uniqueName="12" name="Entradas Total" queryTableFieldId="12"/>
+    <tableColumn id="13" xr3:uid="{CA0D0D81-2959-4048-B568-C2A3ECAE3564}" uniqueName="13" name="Salidas Total" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{7662A870-E3B2-4154-B61C-1FBF71041EC3}" uniqueName="14" name="OcupTotal" queryTableFieldId="14"/>
-    <tableColumn id="15" xr3:uid="{D9DFDC86-A607-4E1A-AC03-BA515BCBAFFD}" uniqueName="15" name="Rechazados" queryTableFieldId="15"/>
+    <tableColumn id="15" xr3:uid="{D9DFDC86-A607-4E1A-AC03-BA515BCBAFFD}" uniqueName="15" name="Rechazados acumulados" queryTableFieldId="15"/>
+    <tableColumn id="17" xr3:uid="{C1FC1DA5-EF45-4471-8849-5F495E3FF680}" uniqueName="17" name="% Utilización Total" queryTableFieldId="17" dataDxfId="103">
+      <calculatedColumnFormula>+output[[#This Row],[OcupTotal]]/264</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{5E209660-3C78-463E-8A28-FB880F017BEF}" uniqueName="18" name="% Utilización Externo" queryTableFieldId="18" dataDxfId="102">
+      <calculatedColumnFormula>+output[[#This Row],[Ocupación Externo]]/100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{A5807F5A-8F30-44BB-AB84-52E671F2A0A3}" uniqueName="19" name="% Utilización Central" queryTableFieldId="19" dataDxfId="101">
+      <calculatedColumnFormula>+output[[#This Row],[Ocupación Central]]/73</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{E58CA651-F54D-4F7B-A992-F3575454629B}" uniqueName="20" name="% Utilización Polideportivo" queryTableFieldId="20" dataDxfId="100">
+      <calculatedColumnFormula>+output[[#This Row],[Ocupación Polideportivo]]/91</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{CBA7D8CD-20EB-41E6-B1A4-A2DEF8230906}" uniqueName="21" name="Rechazados por hora" queryTableFieldId="21" dataDxfId="27">
+      <calculatedColumnFormula>+output[[#This Row],[Rechazados acumulados]]-O1</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -615,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126F70EF-1C35-43D8-8371-85958791E966}">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:T104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -628,13 +1691,14 @@
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="2"/>
     <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,51 +1706,66 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="O1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -712,7 +1791,7 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>26</v>
       </c>
       <c r="L2">
@@ -724,16 +1803,35 @@
       <c r="N2">
         <v>80</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.30303030303030304</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.31</v>
+      </c>
+      <c r="R2" s="4">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.31506849315068491</v>
+      </c>
+      <c r="S2" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -759,7 +1857,7 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>46</v>
       </c>
       <c r="L3">
@@ -774,13 +1872,33 @@
       <c r="O3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
+      <c r="P3" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="Q3" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R3" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.57534246575342463</v>
+      </c>
+      <c r="S3" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.50549450549450547</v>
+      </c>
+      <c r="T3" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4">
         <v>19</v>
@@ -806,7 +1924,7 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>60</v>
       </c>
       <c r="L4">
@@ -821,13 +1939,33 @@
       <c r="O4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
+      <c r="P4" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.73106060606060608</v>
+      </c>
+      <c r="Q4" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.75</v>
+      </c>
+      <c r="R4" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.79452054794520544</v>
+      </c>
+      <c r="S4" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.65934065934065933</v>
+      </c>
+      <c r="T4" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
       <c r="C5">
         <v>23</v>
@@ -853,7 +1991,7 @@
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>67</v>
       </c>
       <c r="L5">
@@ -868,13 +2006,33 @@
       <c r="O5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
+      <c r="P5" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.85227272727272729</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.94</v>
+      </c>
+      <c r="R5" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.87671232876712324</v>
+      </c>
+      <c r="S5" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.73626373626373631</v>
+      </c>
+      <c r="T5" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -900,7 +2058,7 @@
       <c r="J6">
         <v>11</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>71</v>
       </c>
       <c r="L6">
@@ -915,13 +2073,33 @@
       <c r="O6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
+      <c r="P6" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.85984848484848486</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.95</v>
+      </c>
+      <c r="R6" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.83561643835616439</v>
+      </c>
+      <c r="S6" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.78021978021978022</v>
+      </c>
+      <c r="T6" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -947,7 +2125,7 @@
       <c r="J7">
         <v>16</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>64</v>
       </c>
       <c r="L7">
@@ -962,13 +2140,33 @@
       <c r="O7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
+      <c r="P7" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.76515151515151514</v>
+      </c>
+      <c r="Q7" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.85</v>
+      </c>
+      <c r="R7" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.72602739726027399</v>
+      </c>
+      <c r="S7" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.70329670329670335</v>
+      </c>
+      <c r="T7" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -994,7 +2192,7 @@
       <c r="J8">
         <v>17</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>59</v>
       </c>
       <c r="L8">
@@ -1009,13 +2207,33 @@
       <c r="O8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
+      <c r="P8" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.68560606060606055</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.73</v>
+      </c>
+      <c r="R8" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.67123287671232879</v>
+      </c>
+      <c r="S8" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.64835164835164838</v>
+      </c>
+      <c r="T8" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -1041,7 +2259,7 @@
       <c r="J9">
         <v>12</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>61</v>
       </c>
       <c r="L9">
@@ -1056,13 +2274,33 @@
       <c r="O9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
+      <c r="P9" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.64015151515151514</v>
+      </c>
+      <c r="Q9" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.59</v>
+      </c>
+      <c r="R9" s="4">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.67123287671232879</v>
+      </c>
+      <c r="S9" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.67032967032967028</v>
+      </c>
+      <c r="T9" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -1088,7 +2326,7 @@
       <c r="J10">
         <v>16</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>58</v>
       </c>
       <c r="L10">
@@ -1103,13 +2341,33 @@
       <c r="O10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
+      <c r="P10" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.61742424242424243</v>
+      </c>
+      <c r="Q10" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R10" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.67123287671232879</v>
+      </c>
+      <c r="S10" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.63736263736263732</v>
+      </c>
+      <c r="T10" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -1135,7 +2393,7 @@
       <c r="J11">
         <v>13</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>57</v>
       </c>
       <c r="L11">
@@ -1150,13 +2408,33 @@
       <c r="O11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
+      <c r="P11" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q11" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R11" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.64383561643835618</v>
+      </c>
+      <c r="S11" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.62637362637362637</v>
+      </c>
+      <c r="T11" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
       </c>
       <c r="C12">
         <v>33</v>
@@ -1167,7 +2445,7 @@
       <c r="E12">
         <v>78</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>25</v>
       </c>
       <c r="G12">
@@ -1182,7 +2460,7 @@
       <c r="J12">
         <v>10</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>77</v>
       </c>
       <c r="L12">
@@ -1197,13 +2475,33 @@
       <c r="O12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="P12" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.81060606060606055</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.78</v>
+      </c>
+      <c r="R12" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.80821917808219179</v>
+      </c>
+      <c r="S12" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="T12" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C13">
         <v>27</v>
@@ -1229,7 +2527,7 @@
       <c r="J13">
         <v>13</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>91</v>
       </c>
       <c r="L13">
@@ -1244,13 +2542,33 @@
       <c r="O13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>28</v>
+      <c r="P13" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.98106060606060608</v>
+      </c>
+      <c r="Q13" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.98</v>
+      </c>
+      <c r="R13" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.95890410958904104</v>
+      </c>
+      <c r="S13" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T13" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O12</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
       </c>
       <c r="C14">
         <v>11</v>
@@ -1276,7 +2594,7 @@
       <c r="J14">
         <v>14</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>91</v>
       </c>
       <c r="L14">
@@ -1291,13 +2609,33 @@
       <c r="O14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="P14" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S14" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15">
         <v>15</v>
@@ -1323,7 +2661,7 @@
       <c r="J15">
         <v>12</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>91</v>
       </c>
       <c r="L15">
@@ -1338,14 +2676,33 @@
       <c r="O15">
         <v>4</v>
       </c>
-      <c r="Q15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>30</v>
+      <c r="P15" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="Q15" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.92</v>
+      </c>
+      <c r="R15" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T15" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1371,7 +2728,7 @@
       <c r="J16">
         <v>20</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>81</v>
       </c>
       <c r="L16">
@@ -1386,13 +2743,33 @@
       <c r="O16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>31</v>
+      <c r="P16" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.87121212121212122</v>
+      </c>
+      <c r="Q16" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.82</v>
+      </c>
+      <c r="R16" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.9178082191780822</v>
+      </c>
+      <c r="S16" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.89010989010989006</v>
+      </c>
+      <c r="T16" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1433,13 +2810,33 @@
       <c r="O17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>32</v>
+      <c r="P17">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Q17">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.61</v>
+      </c>
+      <c r="R17">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.65753424657534243</v>
+      </c>
+      <c r="S17" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.64835164835164838</v>
+      </c>
+      <c r="T17" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1480,13 +2877,33 @@
       <c r="O18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>34</v>
+      <c r="P18">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.37878787878787878</v>
+      </c>
+      <c r="Q18">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.35</v>
+      </c>
+      <c r="R18">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.42465753424657532</v>
+      </c>
+      <c r="S18" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.37362637362637363</v>
+      </c>
+      <c r="T18" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1527,13 +2944,33 @@
       <c r="O19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>35</v>
+      <c r="P19">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.2196969696969697</v>
+      </c>
+      <c r="Q19">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.2</v>
+      </c>
+      <c r="R19">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.19178082191780821</v>
+      </c>
+      <c r="S19" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.26373626373626374</v>
+      </c>
+      <c r="T19" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1574,13 +3011,33 @@
       <c r="O20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>36</v>
+      <c r="P20">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.11742424242424243</v>
+      </c>
+      <c r="Q20">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.1</v>
+      </c>
+      <c r="R20">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>9.5890410958904104E-2</v>
+      </c>
+      <c r="S20" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="T20" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1621,13 +3078,33 @@
       <c r="O21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>37</v>
+      <c r="P21">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>2.6515151515151516E-2</v>
+      </c>
+      <c r="Q21">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="S21" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>6.5934065934065936E-2</v>
+      </c>
+      <c r="T21" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1668,13 +3145,33 @@
       <c r="O22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
+      <c r="P22">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="Q22">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1.098901098901099E-2</v>
+      </c>
+      <c r="T22" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
       </c>
       <c r="C23">
         <v>29</v>
@@ -1700,7 +3197,7 @@
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>38</v>
       </c>
       <c r="L23">
@@ -1715,13 +3212,33 @@
       <c r="O23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>17</v>
+      <c r="P23" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.32196969696969696</v>
+      </c>
+      <c r="Q23" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R23" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.24657534246575341</v>
+      </c>
+      <c r="S23" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.4175824175824176</v>
+      </c>
+      <c r="T23" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O22</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
       </c>
       <c r="C24">
         <v>32</v>
@@ -1747,7 +3264,7 @@
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>55</v>
       </c>
       <c r="L24">
@@ -1762,13 +3279,33 @@
       <c r="O24">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>18</v>
+      <c r="P24" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.57954545454545459</v>
+      </c>
+      <c r="Q24" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.61</v>
+      </c>
+      <c r="R24" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.50684931506849318</v>
+      </c>
+      <c r="S24" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.60439560439560436</v>
+      </c>
+      <c r="T24" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
       </c>
       <c r="C25">
         <v>17</v>
@@ -1794,7 +3331,7 @@
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>64</v>
       </c>
       <c r="L25">
@@ -1809,13 +3346,33 @@
       <c r="O25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>19</v>
+      <c r="P25" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.71969696969696972</v>
+      </c>
+      <c r="Q25" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.78</v>
+      </c>
+      <c r="R25" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.65753424657534243</v>
+      </c>
+      <c r="S25" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.70329670329670335</v>
+      </c>
+      <c r="T25" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
       </c>
       <c r="C26">
         <v>13</v>
@@ -1841,7 +3398,7 @@
       <c r="J26">
         <v>6</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>69</v>
       </c>
       <c r="L26">
@@ -1856,13 +3413,33 @@
       <c r="O26">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
+      <c r="P26" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="Q26" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.86</v>
+      </c>
+      <c r="R26" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.72602739726027399</v>
+      </c>
+      <c r="S26" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.75824175824175821</v>
+      </c>
+      <c r="T26" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
       </c>
       <c r="C27">
         <v>18</v>
@@ -1888,7 +3465,7 @@
       <c r="J27">
         <v>14</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>64</v>
       </c>
       <c r="L27">
@@ -1903,13 +3480,33 @@
       <c r="O27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="P27" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.78030303030303028</v>
+      </c>
+      <c r="Q27" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.86</v>
+      </c>
+      <c r="R27" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.76712328767123283</v>
+      </c>
+      <c r="S27" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.70329670329670335</v>
+      </c>
+      <c r="T27" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -1935,7 +3532,7 @@
       <c r="J28">
         <v>17</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>57</v>
       </c>
       <c r="L28">
@@ -1950,13 +3547,33 @@
       <c r="O28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>22</v>
+      <c r="P28" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.70454545454545459</v>
+      </c>
+      <c r="Q28" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.78</v>
+      </c>
+      <c r="R28" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.69863013698630139</v>
+      </c>
+      <c r="S28" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.62637362637362637</v>
+      </c>
+      <c r="T28" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -1982,7 +3599,7 @@
       <c r="J29">
         <v>15</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>50</v>
       </c>
       <c r="L29">
@@ -1997,13 +3614,33 @@
       <c r="O29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>23</v>
+      <c r="P29" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.625</v>
+      </c>
+      <c r="Q29" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.74</v>
+      </c>
+      <c r="R29" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.56164383561643838</v>
+      </c>
+      <c r="S29" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="T29" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -2029,7 +3666,7 @@
       <c r="J30">
         <v>16</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="2">
         <v>55</v>
       </c>
       <c r="L30">
@@ -2044,13 +3681,33 @@
       <c r="O30">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>24</v>
+      <c r="P30" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="Q30" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.64</v>
+      </c>
+      <c r="R30" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.58904109589041098</v>
+      </c>
+      <c r="S30" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.60439560439560436</v>
+      </c>
+      <c r="T30" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
       </c>
       <c r="C31">
         <v>15</v>
@@ -2076,7 +3733,7 @@
       <c r="J31">
         <v>11</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="2">
         <v>57</v>
       </c>
       <c r="L31">
@@ -2091,13 +3748,33 @@
       <c r="O31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>25</v>
+      <c r="P31" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Q31" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.61</v>
+      </c>
+      <c r="R31" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.49315068493150682</v>
+      </c>
+      <c r="S31" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.62637362637362637</v>
+      </c>
+      <c r="T31" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
       </c>
       <c r="C32">
         <v>13</v>
@@ -2123,7 +3800,7 @@
       <c r="J32">
         <v>8</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="2">
         <v>65</v>
       </c>
       <c r="L32">
@@ -2138,13 +3815,33 @@
       <c r="O32">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>26</v>
+      <c r="P32" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="Q32" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R32" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.56164383561643838</v>
+      </c>
+      <c r="S32" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T32" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
       </c>
       <c r="C33">
         <v>33</v>
@@ -2170,7 +3867,7 @@
       <c r="J33">
         <v>13</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="2">
         <v>88</v>
       </c>
       <c r="L33">
@@ -2185,13 +3882,33 @@
       <c r="O33">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>27</v>
+      <c r="P33" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.84469696969696972</v>
+      </c>
+      <c r="Q33" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.73</v>
+      </c>
+      <c r="R33" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.84931506849315064</v>
+      </c>
+      <c r="S33" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.96703296703296704</v>
+      </c>
+      <c r="T33" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O32</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
       </c>
       <c r="C34">
         <v>35</v>
@@ -2217,7 +3934,7 @@
       <c r="J34">
         <v>12</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="2">
         <v>91</v>
       </c>
       <c r="L34">
@@ -2232,13 +3949,33 @@
       <c r="O34">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>28</v>
+      <c r="P34" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.99242424242424243</v>
+      </c>
+      <c r="Q34" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.98</v>
+      </c>
+      <c r="R34" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S34" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T34" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O33</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
       </c>
       <c r="C35">
         <v>14</v>
@@ -2264,7 +4001,7 @@
       <c r="J35">
         <v>8</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="2">
         <v>91</v>
       </c>
       <c r="L35">
@@ -2279,13 +4016,33 @@
       <c r="O35">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>29</v>
+      <c r="P35" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q35" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R35" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S35" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T35" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
       </c>
       <c r="C36">
         <v>15</v>
@@ -2311,7 +4068,7 @@
       <c r="J36">
         <v>18</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="2">
         <v>91</v>
       </c>
       <c r="L36">
@@ -2326,13 +4083,33 @@
       <c r="O36">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>30</v>
+      <c r="P36" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R36" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S36" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T36" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
       </c>
       <c r="C37">
         <v>13</v>
@@ -2358,7 +4135,7 @@
       <c r="J37">
         <v>32</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="2">
         <v>81</v>
       </c>
       <c r="L37">
@@ -2373,13 +4150,33 @@
       <c r="O37">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>31</v>
+      <c r="P37" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.94318181818181823</v>
+      </c>
+      <c r="Q37" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.95</v>
+      </c>
+      <c r="R37" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S37" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.89010989010989006</v>
+      </c>
+      <c r="T37" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2420,13 +4217,33 @@
       <c r="O38">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>32</v>
+      <c r="P38">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.71969696969696972</v>
+      </c>
+      <c r="Q38">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.69</v>
+      </c>
+      <c r="R38">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.75342465753424659</v>
+      </c>
+      <c r="S38" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.72527472527472525</v>
+      </c>
+      <c r="T38" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2467,13 +4284,33 @@
       <c r="O39">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>34</v>
+      <c r="P39">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.47348484848484851</v>
+      </c>
+      <c r="Q39">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.45</v>
+      </c>
+      <c r="R39">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.46575342465753422</v>
+      </c>
+      <c r="S39" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.50549450549450547</v>
+      </c>
+      <c r="T39" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2514,13 +4351,33 @@
       <c r="O40">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>35</v>
+      <c r="P40">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.30681818181818182</v>
+      </c>
+      <c r="Q40">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.26</v>
+      </c>
+      <c r="R40">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.36986301369863012</v>
+      </c>
+      <c r="S40" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="T40" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2561,13 +4418,33 @@
       <c r="O41">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>36</v>
+      <c r="P41">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.16287878787878787</v>
+      </c>
+      <c r="Q41">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.18</v>
+      </c>
+      <c r="R41">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.15068493150684931</v>
+      </c>
+      <c r="S41" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="T41" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2608,13 +4485,33 @@
       <c r="O42">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>37</v>
+      <c r="P42">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="Q42">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.05</v>
+      </c>
+      <c r="R42">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>5.4794520547945202E-2</v>
+      </c>
+      <c r="S42" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="T42" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2655,13 +4552,33 @@
       <c r="O43">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>39</v>
+      <c r="P43">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="Q43">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="R43">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="S43" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1.098901098901099E-2</v>
+      </c>
+      <c r="T43" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2702,13 +4619,33 @@
       <c r="O44">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>40</v>
+      <c r="P44">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>7.575757575757576E-3</v>
+      </c>
+      <c r="Q44">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="S44" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1.098901098901099E-2</v>
+      </c>
+      <c r="T44" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2749,13 +4686,33 @@
       <c r="O45">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>16</v>
+      <c r="P45">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="Q45">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="S45" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T45" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
       </c>
       <c r="C46">
         <v>28</v>
@@ -2781,7 +4738,7 @@
       <c r="J46">
         <v>0</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="2">
         <v>21</v>
       </c>
       <c r="L46">
@@ -2796,13 +4753,33 @@
       <c r="O46">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>17</v>
+      <c r="P46" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="Q46" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R46" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.38356164383561642</v>
+      </c>
+      <c r="S46" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="T46" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O45</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
       </c>
       <c r="C47">
         <v>37</v>
@@ -2828,7 +4805,7 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="2">
         <v>46</v>
       </c>
       <c r="L47">
@@ -2843,13 +4820,33 @@
       <c r="O47">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>18</v>
+      <c r="P47" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="Q47" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.65</v>
+      </c>
+      <c r="R47" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.69863013698630139</v>
+      </c>
+      <c r="S47" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.50549450549450547</v>
+      </c>
+      <c r="T47" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
       </c>
       <c r="C48">
         <v>13</v>
@@ -2875,7 +4872,7 @@
       <c r="J48">
         <v>0</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="2">
         <v>63</v>
       </c>
       <c r="L48">
@@ -2890,13 +4887,33 @@
       <c r="O48">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>19</v>
+      <c r="P48" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.75</v>
+      </c>
+      <c r="Q48" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.78</v>
+      </c>
+      <c r="R48" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.78082191780821919</v>
+      </c>
+      <c r="S48" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="T48" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
       </c>
       <c r="C49">
         <v>15</v>
@@ -2922,7 +4939,7 @@
       <c r="J49">
         <v>5</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="2">
         <v>73</v>
       </c>
       <c r="L49">
@@ -2937,13 +4954,33 @@
       <c r="O49">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>20</v>
+      <c r="P49" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.84090909090909094</v>
+      </c>
+      <c r="Q49" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.89</v>
+      </c>
+      <c r="R49" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.82191780821917804</v>
+      </c>
+      <c r="S49" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.80219780219780223</v>
+      </c>
+      <c r="T49" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
       </c>
       <c r="C50">
         <v>20</v>
@@ -2969,7 +5006,7 @@
       <c r="J50">
         <v>9</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="2">
         <v>77</v>
       </c>
       <c r="L50">
@@ -2984,13 +5021,33 @@
       <c r="O50">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>21</v>
+      <c r="P50" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.85227272727272729</v>
+      </c>
+      <c r="Q50" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.94</v>
+      </c>
+      <c r="R50" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.73972602739726023</v>
+      </c>
+      <c r="S50" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="T50" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>9</v>
       </c>
       <c r="C51">
         <v>8</v>
@@ -3016,7 +5073,7 @@
       <c r="J51">
         <v>11</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="2">
         <v>73</v>
       </c>
       <c r="L51">
@@ -3031,13 +5088,33 @@
       <c r="O51">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>22</v>
+      <c r="P51" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.78030303030303028</v>
+      </c>
+      <c r="Q51" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.82</v>
+      </c>
+      <c r="R51" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.69863013698630139</v>
+      </c>
+      <c r="S51" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.80219780219780223</v>
+      </c>
+      <c r="T51" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -3063,7 +5140,7 @@
       <c r="J52">
         <v>29</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="2">
         <v>50</v>
       </c>
       <c r="L52">
@@ -3078,13 +5155,33 @@
       <c r="O52">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>23</v>
+      <c r="P52" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.63257575757575757</v>
+      </c>
+      <c r="Q52" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.74</v>
+      </c>
+      <c r="R52" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.58904109589041098</v>
+      </c>
+      <c r="S52" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="T52" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
       </c>
       <c r="C53">
         <v>11</v>
@@ -3110,7 +5207,7 @@
       <c r="J53">
         <v>17</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="2">
         <v>44</v>
       </c>
       <c r="L53">
@@ -3125,13 +5222,33 @@
       <c r="O53">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>24</v>
+      <c r="P53" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.55681818181818177</v>
+      </c>
+      <c r="Q53" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.63</v>
+      </c>
+      <c r="R53" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.54794520547945202</v>
+      </c>
+      <c r="S53" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.48351648351648352</v>
+      </c>
+      <c r="T53" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
       </c>
       <c r="C54">
         <v>9</v>
@@ -3157,7 +5274,7 @@
       <c r="J54">
         <v>11</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="2">
         <v>50</v>
       </c>
       <c r="L54">
@@ -3172,13 +5289,33 @@
       <c r="O54">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>25</v>
+      <c r="P54" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.53787878787878785</v>
+      </c>
+      <c r="Q54" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.52</v>
+      </c>
+      <c r="R54" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.54794520547945202</v>
+      </c>
+      <c r="S54" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.5494505494505495</v>
+      </c>
+      <c r="T54" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
       </c>
       <c r="C55">
         <v>19</v>
@@ -3204,7 +5341,7 @@
       <c r="J55">
         <v>11</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="2">
         <v>46</v>
       </c>
       <c r="L55">
@@ -3219,13 +5356,33 @@
       <c r="O55">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="P55" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="Q55" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R55" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.56164383561643838</v>
+      </c>
+      <c r="S55" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.50549450549450547</v>
+      </c>
+      <c r="T55" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
       </c>
       <c r="C56">
         <v>31</v>
@@ -3251,7 +5408,7 @@
       <c r="J56">
         <v>6</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="2">
         <v>69</v>
       </c>
       <c r="L56">
@@ -3266,13 +5423,33 @@
       <c r="O56">
         <v>19</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>27</v>
+      <c r="P56" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.76893939393939392</v>
+      </c>
+      <c r="Q56" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.74</v>
+      </c>
+      <c r="R56" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.82191780821917804</v>
+      </c>
+      <c r="S56" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.75824175824175821</v>
+      </c>
+      <c r="T56" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O55</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
       </c>
       <c r="C57">
         <v>32</v>
@@ -3298,7 +5475,7 @@
       <c r="J57">
         <v>10</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="2">
         <v>91</v>
       </c>
       <c r="L57">
@@ -3313,13 +5490,33 @@
       <c r="O57">
         <v>22</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>28</v>
+      <c r="P57" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.99621212121212122</v>
+      </c>
+      <c r="Q57" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.99</v>
+      </c>
+      <c r="R57" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S57" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T57" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O56</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -3345,7 +5542,7 @@
       <c r="J58">
         <v>9</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="2">
         <v>91</v>
       </c>
       <c r="L58">
@@ -3360,13 +5557,33 @@
       <c r="O58">
         <v>22</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>29</v>
+      <c r="P58" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q58" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R58" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S58" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T58" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
       </c>
       <c r="C59">
         <v>9</v>
@@ -3392,7 +5609,7 @@
       <c r="J59">
         <v>13</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="2">
         <v>91</v>
       </c>
       <c r="L59">
@@ -3407,13 +5624,33 @@
       <c r="O59">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>30</v>
+      <c r="P59" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q59" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R59" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S59" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T59" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
       </c>
       <c r="C60">
         <v>19</v>
@@ -3439,7 +5676,7 @@
       <c r="J60">
         <v>22</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="2">
         <v>79</v>
       </c>
       <c r="L60">
@@ -3454,13 +5691,33 @@
       <c r="O60">
         <v>22</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>31</v>
+      <c r="P60" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="Q60" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R60" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S60" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.86813186813186816</v>
+      </c>
+      <c r="T60" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -3501,13 +5758,33 @@
       <c r="O61">
         <v>22</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>32</v>
+      <c r="P61">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.73106060606060608</v>
+      </c>
+      <c r="Q61">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.75</v>
+      </c>
+      <c r="R61">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.86301369863013699</v>
+      </c>
+      <c r="S61" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.60439560439560436</v>
+      </c>
+      <c r="T61" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s">
+        <v>20</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3548,13 +5825,33 @@
       <c r="O62">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>34</v>
+      <c r="P62">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.51893939393939392</v>
+      </c>
+      <c r="Q62">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.52</v>
+      </c>
+      <c r="R62">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.58904109589041098</v>
+      </c>
+      <c r="S62" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="T62" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" t="s">
+        <v>22</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3595,13 +5892,33 @@
       <c r="O63">
         <v>22</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>35</v>
+      <c r="P63">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.34848484848484851</v>
+      </c>
+      <c r="Q63">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.35</v>
+      </c>
+      <c r="R63">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.41095890410958902</v>
+      </c>
+      <c r="S63" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="T63" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3642,13 +5959,33 @@
       <c r="O64">
         <v>22</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>36</v>
+      <c r="P64">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.14772727272727273</v>
+      </c>
+      <c r="Q64">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.13</v>
+      </c>
+      <c r="R64">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.24657534246575341</v>
+      </c>
+      <c r="S64" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>8.7912087912087919E-2</v>
+      </c>
+      <c r="T64" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3689,13 +6026,33 @@
       <c r="O65">
         <v>22</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>37</v>
+      <c r="P65">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>5.3030303030303032E-2</v>
+      </c>
+      <c r="Q65">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.06</v>
+      </c>
+      <c r="R65">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>6.8493150684931503E-2</v>
+      </c>
+      <c r="S65" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>3.2967032967032968E-2</v>
+      </c>
+      <c r="T65" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3736,13 +6093,33 @@
       <c r="O66">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>39</v>
+      <c r="P66">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1.893939393939394E-2</v>
+      </c>
+      <c r="Q66">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.03</v>
+      </c>
+      <c r="R66">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>2.7397260273972601E-2</v>
+      </c>
+      <c r="S66" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T66" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" t="s">
+        <v>27</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3783,13 +6160,33 @@
       <c r="O67">
         <v>22</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>16</v>
+      <c r="P67">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="Q67">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="R67">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0</v>
+      </c>
+      <c r="S67" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T67" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
       </c>
       <c r="C68">
         <v>39</v>
@@ -3815,7 +6212,7 @@
       <c r="J68">
         <v>0</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="2">
         <v>24</v>
       </c>
       <c r="L68">
@@ -3830,13 +6227,33 @@
       <c r="O68">
         <v>24</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>17</v>
+      <c r="P68" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.32575757575757575</v>
+      </c>
+      <c r="Q68" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.39</v>
+      </c>
+      <c r="R68" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.31506849315068491</v>
+      </c>
+      <c r="S68" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.26373626373626374</v>
+      </c>
+      <c r="T68" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O67</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
       </c>
       <c r="C69">
         <v>21</v>
@@ -3862,7 +6279,7 @@
       <c r="J69">
         <v>0</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="2">
         <v>45</v>
       </c>
       <c r="L69">
@@ -3877,13 +6294,33 @@
       <c r="O69">
         <v>25</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>18</v>
+      <c r="P69" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="Q69" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.6</v>
+      </c>
+      <c r="R69" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.52054794520547942</v>
+      </c>
+      <c r="S69" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.49450549450549453</v>
+      </c>
+      <c r="T69" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O68</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
       </c>
       <c r="C70">
         <v>16</v>
@@ -3909,7 +6346,7 @@
       <c r="J70">
         <v>0</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="2">
         <v>63</v>
       </c>
       <c r="L70">
@@ -3924,13 +6361,33 @@
       <c r="O70">
         <v>26</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>19</v>
+      <c r="P70" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.69318181818181823</v>
+      </c>
+      <c r="Q70" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.76</v>
+      </c>
+      <c r="R70" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.60273972602739723</v>
+      </c>
+      <c r="S70" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="T70" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O69</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
       </c>
       <c r="C71">
         <v>15</v>
@@ -3956,7 +6413,7 @@
       <c r="J71">
         <v>8</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="2">
         <v>72</v>
       </c>
       <c r="L71">
@@ -3971,13 +6428,33 @@
       <c r="O71">
         <v>26</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>20</v>
+      <c r="P71" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="Q71" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.83</v>
+      </c>
+      <c r="R71" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.72602739726027399</v>
+      </c>
+      <c r="S71" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.79120879120879117</v>
+      </c>
+      <c r="T71" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
       </c>
       <c r="C72">
         <v>9</v>
@@ -4003,7 +6480,7 @@
       <c r="J72">
         <v>8</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="2">
         <v>76</v>
       </c>
       <c r="L72">
@@ -4018,13 +6495,33 @@
       <c r="O72">
         <v>28</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>21</v>
+      <c r="P72" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.80681818181818177</v>
+      </c>
+      <c r="Q72" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.81</v>
+      </c>
+      <c r="R72" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.76712328767123283</v>
+      </c>
+      <c r="S72" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.8351648351648352</v>
+      </c>
+      <c r="T72" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O71</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" t="s">
+        <v>9</v>
       </c>
       <c r="C73">
         <v>6</v>
@@ -4050,7 +6547,7 @@
       <c r="J73">
         <v>18</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="2">
         <v>63</v>
       </c>
       <c r="L73">
@@ -4065,13 +6562,33 @@
       <c r="O73">
         <v>28</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>22</v>
+      <c r="P73" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="Q73" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.7</v>
+      </c>
+      <c r="R73" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.73972602739726023</v>
+      </c>
+      <c r="S73" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="T73" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
       </c>
       <c r="C74">
         <v>7</v>
@@ -4097,7 +6614,7 @@
       <c r="J74">
         <v>15</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="2">
         <v>59</v>
       </c>
       <c r="L74">
@@ -4112,13 +6629,33 @@
       <c r="O74">
         <v>28</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>23</v>
+      <c r="P74" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.625</v>
+      </c>
+      <c r="Q74" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.64</v>
+      </c>
+      <c r="R74" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.57534246575342463</v>
+      </c>
+      <c r="S74" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.64835164835164838</v>
+      </c>
+      <c r="T74" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
       </c>
       <c r="C75">
         <v>15</v>
@@ -4144,7 +6681,7 @@
       <c r="J75">
         <v>17</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="2">
         <v>56</v>
       </c>
       <c r="L75">
@@ -4159,13 +6696,33 @@
       <c r="O75">
         <v>28</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>24</v>
+      <c r="P75" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="Q75" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.59</v>
+      </c>
+      <c r="R75" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.64383561643835618</v>
+      </c>
+      <c r="S75" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="T75" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
       </c>
       <c r="C76">
         <v>9</v>
@@ -4191,7 +6748,7 @@
       <c r="J76">
         <v>11</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="2">
         <v>61</v>
       </c>
       <c r="L76">
@@ -4206,13 +6763,33 @@
       <c r="O76">
         <v>28</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>25</v>
+      <c r="P76" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.59469696969696972</v>
+      </c>
+      <c r="Q76" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.54</v>
+      </c>
+      <c r="R76" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.57534246575342463</v>
+      </c>
+      <c r="S76" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.67032967032967028</v>
+      </c>
+      <c r="T76" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" t="s">
+        <v>13</v>
       </c>
       <c r="C77">
         <v>16</v>
@@ -4238,7 +6815,7 @@
       <c r="J77">
         <v>14</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="2">
         <v>70</v>
       </c>
       <c r="L77">
@@ -4253,13 +6830,33 @@
       <c r="O77">
         <v>31</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>26</v>
+      <c r="P77" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="Q77" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R77" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.75342465753424659</v>
+      </c>
+      <c r="S77" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="T77" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O76</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
       </c>
       <c r="C78">
         <v>29</v>
@@ -4285,7 +6882,7 @@
       <c r="J78">
         <v>10</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="2">
         <v>85</v>
       </c>
       <c r="L78">
@@ -4300,13 +6897,33 @@
       <c r="O78">
         <v>32</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>27</v>
+      <c r="P78" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.84848484848484851</v>
+      </c>
+      <c r="Q78" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.74</v>
+      </c>
+      <c r="R78" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.8904109589041096</v>
+      </c>
+      <c r="S78" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.93406593406593408</v>
+      </c>
+      <c r="T78" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O77</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>29</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
       </c>
       <c r="C79">
         <v>23</v>
@@ -4332,7 +6949,7 @@
       <c r="J79">
         <v>8</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="2">
         <v>91</v>
       </c>
       <c r="L79">
@@ -4347,13 +6964,33 @@
       <c r="O79">
         <v>33</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>28</v>
+      <c r="P79" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.9507575757575758</v>
+      </c>
+      <c r="Q79" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.87</v>
+      </c>
+      <c r="R79" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S79" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T79" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O78</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
       </c>
       <c r="C80">
         <v>12</v>
@@ -4379,7 +7016,7 @@
       <c r="J80">
         <v>18</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="2">
         <v>91</v>
       </c>
       <c r="L80">
@@ -4394,13 +7031,33 @@
       <c r="O80">
         <v>34</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="P80" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.97348484848484851</v>
+      </c>
+      <c r="Q80" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.93</v>
+      </c>
+      <c r="R80" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S80" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T80" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O79</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>29</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
       </c>
       <c r="C81">
         <v>12</v>
@@ -4426,7 +7083,7 @@
       <c r="J81">
         <v>13</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="2">
         <v>91</v>
       </c>
       <c r="L81">
@@ -4441,13 +7098,33 @@
       <c r="O81">
         <v>34</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>30</v>
+      <c r="P81" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.96590909090909094</v>
+      </c>
+      <c r="Q81" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.91</v>
+      </c>
+      <c r="R81" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S81" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T81" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
       </c>
       <c r="C82">
         <v>9</v>
@@ -4473,7 +7150,7 @@
       <c r="J82">
         <v>23</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="2">
         <v>74</v>
       </c>
       <c r="L82">
@@ -4488,13 +7165,33 @@
       <c r="O82">
         <v>34</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>31</v>
+      <c r="P82" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.73863636363636365</v>
+      </c>
+      <c r="Q82" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.73</v>
+      </c>
+      <c r="R82" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.65753424657534243</v>
+      </c>
+      <c r="S82" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.81318681318681318</v>
+      </c>
+      <c r="T82" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" t="s">
+        <v>19</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -4535,13 +7232,33 @@
       <c r="O83">
         <v>34</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>32</v>
+      <c r="P83">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.52651515151515149</v>
+      </c>
+      <c r="Q83">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.49</v>
+      </c>
+      <c r="R83">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.49315068493150682</v>
+      </c>
+      <c r="S83" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.59340659340659341</v>
+      </c>
+      <c r="T83" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -4582,13 +7299,33 @@
       <c r="O84">
         <v>34</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>34</v>
+      <c r="P84">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.34469696969696972</v>
+      </c>
+      <c r="Q84">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R84">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.38356164383561642</v>
+      </c>
+      <c r="S84" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.37362637362637363</v>
+      </c>
+      <c r="T84" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>22</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4629,13 +7366,33 @@
       <c r="O85">
         <v>34</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>35</v>
+      <c r="P85">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="Q85">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.16</v>
+      </c>
+      <c r="R85">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.20547945205479451</v>
+      </c>
+      <c r="S85" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.18681318681318682</v>
+      </c>
+      <c r="T85" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>23</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4676,13 +7433,33 @@
       <c r="O86">
         <v>34</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>36</v>
+      <c r="P86">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>7.575757575757576E-2</v>
+      </c>
+      <c r="Q86">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.09</v>
+      </c>
+      <c r="R86">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>2.7397260273972601E-2</v>
+      </c>
+      <c r="S86" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>9.8901098901098897E-2</v>
+      </c>
+      <c r="T86" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4723,13 +7500,33 @@
       <c r="O87">
         <v>34</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>37</v>
+      <c r="P87">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Q87">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R87">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="S87" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>3.2967032967032968E-2</v>
+      </c>
+      <c r="T87" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4770,13 +7567,33 @@
       <c r="O88">
         <v>34</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>39</v>
+      <c r="P88">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1.1363636363636364E-2</v>
+      </c>
+      <c r="Q88">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.03</v>
+      </c>
+      <c r="R88">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0</v>
+      </c>
+      <c r="S88" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T88" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4817,13 +7634,33 @@
       <c r="O89">
         <v>34</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>16</v>
+      <c r="P89">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="Q89">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="R89">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0</v>
+      </c>
+      <c r="S89" s="5">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T89" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
       </c>
       <c r="C90">
         <v>28</v>
@@ -4849,7 +7686,7 @@
       <c r="J90">
         <v>0</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="2">
         <v>35</v>
       </c>
       <c r="L90">
@@ -4864,13 +7701,33 @@
       <c r="O90">
         <v>36</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>17</v>
+      <c r="P90" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.32196969696969696</v>
+      </c>
+      <c r="Q90" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R90" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.30136986301369861</v>
+      </c>
+      <c r="S90" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="T90" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O89</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>5</v>
       </c>
       <c r="C91">
         <v>21</v>
@@ -4896,7 +7753,7 @@
       <c r="J91">
         <v>0</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="2">
         <v>61</v>
       </c>
       <c r="L91">
@@ -4911,13 +7768,33 @@
       <c r="O91">
         <v>36</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>18</v>
+      <c r="P91" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="Q91" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.49</v>
+      </c>
+      <c r="R91" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.46575342465753422</v>
+      </c>
+      <c r="S91" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.67032967032967028</v>
+      </c>
+      <c r="T91" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
       </c>
       <c r="C92">
         <v>11</v>
@@ -4943,7 +7820,7 @@
       <c r="J92">
         <v>1</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="2">
         <v>71</v>
       </c>
       <c r="L92">
@@ -4958,13 +7835,33 @@
       <c r="O92">
         <v>36</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>19</v>
+      <c r="P92" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.64772727272727271</v>
+      </c>
+      <c r="Q92" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.6</v>
+      </c>
+      <c r="R92" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.54794520547945202</v>
+      </c>
+      <c r="S92" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.78021978021978022</v>
+      </c>
+      <c r="T92" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>7</v>
       </c>
       <c r="C93">
         <v>17</v>
@@ -4990,7 +7887,7 @@
       <c r="J93">
         <v>1</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="2">
         <v>81</v>
       </c>
       <c r="L93">
@@ -5005,13 +7902,33 @@
       <c r="O93">
         <v>37</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>20</v>
+      <c r="P93" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.76893939393939392</v>
+      </c>
+      <c r="Q93" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.7</v>
+      </c>
+      <c r="R93" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.71232876712328763</v>
+      </c>
+      <c r="S93" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.89010989010989006</v>
+      </c>
+      <c r="T93" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O92</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>8</v>
       </c>
       <c r="C94">
         <v>10</v>
@@ -5037,7 +7954,7 @@
       <c r="J94">
         <v>12</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="2">
         <v>82</v>
       </c>
       <c r="L94">
@@ -5052,13 +7969,33 @@
       <c r="O94">
         <v>37</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>21</v>
+      <c r="P94" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.78409090909090906</v>
+      </c>
+      <c r="Q94" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.72</v>
+      </c>
+      <c r="R94" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.72602739726027399</v>
+      </c>
+      <c r="S94" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.90109890109890112</v>
+      </c>
+      <c r="T94" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>9</v>
       </c>
       <c r="C95">
         <v>6</v>
@@ -5084,7 +8021,7 @@
       <c r="J95">
         <v>20</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="2">
         <v>75</v>
       </c>
       <c r="L95">
@@ -5099,13 +8036,33 @@
       <c r="O95">
         <v>37</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>22</v>
+      <c r="P95" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.66287878787878785</v>
+      </c>
+      <c r="Q95" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R95" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.60273972602739723</v>
+      </c>
+      <c r="S95" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.82417582417582413</v>
+      </c>
+      <c r="T95" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
       </c>
       <c r="C96">
         <v>10</v>
@@ -5131,7 +8088,7 @@
       <c r="J96">
         <v>19</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="2">
         <v>62</v>
       </c>
       <c r="L96">
@@ -5146,13 +8103,33 @@
       <c r="O96">
         <v>37</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>23</v>
+      <c r="P96" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.57196969696969702</v>
+      </c>
+      <c r="Q96" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.49</v>
+      </c>
+      <c r="R96" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.54794520547945202</v>
+      </c>
+      <c r="S96" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.68131868131868134</v>
+      </c>
+      <c r="T96" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -5178,7 +8155,7 @@
       <c r="J97">
         <v>16</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="2">
         <v>65</v>
       </c>
       <c r="L97">
@@ -5193,13 +8170,33 @@
       <c r="O97">
         <v>37</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>24</v>
+      <c r="P97" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="Q97" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.41</v>
+      </c>
+      <c r="R97" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.50684931506849318</v>
+      </c>
+      <c r="S97" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T97" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -5225,7 +8222,7 @@
       <c r="J98">
         <v>13</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="2">
         <v>65</v>
       </c>
       <c r="L98">
@@ -5240,13 +8237,33 @@
       <c r="O98">
         <v>37</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>25</v>
+      <c r="P98" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.49242424242424243</v>
+      </c>
+      <c r="Q98" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.36</v>
+      </c>
+      <c r="R98" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.39726027397260272</v>
+      </c>
+      <c r="S98" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T98" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
       </c>
       <c r="C99">
         <v>11</v>
@@ -5272,7 +8289,7 @@
       <c r="J99">
         <v>14</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="2">
         <v>72</v>
       </c>
       <c r="L99">
@@ -5287,13 +8304,33 @@
       <c r="O99">
         <v>37</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>26</v>
+      <c r="P99" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.53787878787878785</v>
+      </c>
+      <c r="Q99" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="R99" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.45205479452054792</v>
+      </c>
+      <c r="S99" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.79120879120879117</v>
+      </c>
+      <c r="T99" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" t="s">
+        <v>14</v>
       </c>
       <c r="C100">
         <v>35</v>
@@ -5319,7 +8356,7 @@
       <c r="J100">
         <v>17</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="2">
         <v>86</v>
       </c>
       <c r="L100">
@@ -5334,13 +8371,33 @@
       <c r="O100">
         <v>44</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>27</v>
+      <c r="P100" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.76893939393939392</v>
+      </c>
+      <c r="Q100" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.66</v>
+      </c>
+      <c r="R100" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.69863013698630139</v>
+      </c>
+      <c r="S100" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0.94505494505494503</v>
+      </c>
+      <c r="T100" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O99</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" t="s">
+        <v>15</v>
       </c>
       <c r="C101">
         <v>30</v>
@@ -5366,7 +8423,7 @@
       <c r="J101">
         <v>12</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="2">
         <v>91</v>
       </c>
       <c r="L101">
@@ -5381,13 +8438,33 @@
       <c r="O101">
         <v>47</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>28</v>
+      <c r="P101" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.91287878787878785</v>
+      </c>
+      <c r="Q101" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.89</v>
+      </c>
+      <c r="R101" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.83561643835616439</v>
+      </c>
+      <c r="S101" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T101" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O100</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
       </c>
       <c r="C102">
         <v>9</v>
@@ -5413,7 +8490,7 @@
       <c r="J102">
         <v>17</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="2">
         <v>91</v>
       </c>
       <c r="L102">
@@ -5428,13 +8505,33 @@
       <c r="O102">
         <v>47</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>29</v>
+      <c r="P102" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.93181818181818177</v>
+      </c>
+      <c r="Q102" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.93</v>
+      </c>
+      <c r="R102" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.84931506849315064</v>
+      </c>
+      <c r="S102" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T102" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
       </c>
       <c r="C103">
         <v>14</v>
@@ -5460,7 +8557,7 @@
       <c r="J103">
         <v>12</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="2">
         <v>91</v>
       </c>
       <c r="L103">
@@ -5475,13 +8572,33 @@
       <c r="O103">
         <v>47</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B104" s="1" t="s">
+      <c r="P103" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.93560606060606055</v>
+      </c>
+      <c r="Q103" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.96</v>
+      </c>
+      <c r="R103" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.82191780821917804</v>
+      </c>
+      <c r="S103" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T103" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>30</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
       </c>
       <c r="C104">
         <v>5</v>
@@ -5507,7 +8624,7 @@
       <c r="J104">
         <v>7</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="2">
         <v>91</v>
       </c>
       <c r="L104">
@@ -5522,8 +8639,101 @@
       <c r="O104">
         <v>47</v>
       </c>
+      <c r="P104" s="4">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>0.90530303030303028</v>
+      </c>
+      <c r="Q104" s="3">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>0.9</v>
+      </c>
+      <c r="R104" s="3">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>0.79452054794520544</v>
+      </c>
+      <c r="S104" s="3">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T104" s="5">
+        <f>+output[[#This Row],[Rechazados acumulados]]-O103</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N104">
+    <cfRule type="cellIs" dxfId="26" priority="14" operator="equal">
+      <formula>264</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+      <formula>73</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="cellIs" dxfId="23" priority="11" operator="equal">
+      <formula>91</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:P1048576">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="between">
+      <formula>0.5</formula>
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P1048576">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="greaterThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1:Q1048576">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="between">
+      <formula>0.5</formula>
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q1048576">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R1048576">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="between">
+      <formula>0.5</formula>
+      <formula>0.75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="greaterThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S1048576">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="between">
+      <formula>0.5</formula>
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S104">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="between">
+      <formula>0.5</formula>
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S104">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T104">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Tabla_Resultados_Corrida.xlsx
+++ b/Tabla_Resultados_Corrida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Models\mi-proyecto-anylogic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFB0AF7-A730-4F0B-A59D-03C43D4D0F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163E4BA4-AE9D-457D-9F40-2D9BD1F9366C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A923D075-8E6E-4AD4-8B2A-316AD42E9CB3}"/>
   </bookViews>
@@ -237,38 +237,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="106">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -276,16 +253,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -421,56 +388,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -516,19 +433,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -753,494 +657,7 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1326,8 +743,8 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{29BADEF3-00F3-4923-9B25-9276A2AB6AF3}" uniqueName="1" name="Dia" queryTableFieldId="1" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{7FF5DB85-B9DE-4A5F-8C22-4E66327D084E}" uniqueName="2" name="Hora" queryTableFieldId="2" dataDxfId="104"/>
+    <tableColumn id="1" xr3:uid="{29BADEF3-00F3-4923-9B25-9276A2AB6AF3}" uniqueName="1" name="Dia" queryTableFieldId="1" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{7FF5DB85-B9DE-4A5F-8C22-4E66327D084E}" uniqueName="2" name="Hora" queryTableFieldId="2" dataDxfId="46"/>
     <tableColumn id="3" xr3:uid="{06DDC69D-1405-41D2-A484-702BD6EB6B49}" uniqueName="3" name="Entradas Externo" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{EF2FE910-1170-47C3-9301-CB1EDF69007F}" uniqueName="4" name="Salidas Externo" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{CDF657CF-72AD-48AD-A9F4-18C306027810}" uniqueName="5" name="Ocupación Externo" queryTableFieldId="5"/>
@@ -1341,19 +758,19 @@
     <tableColumn id="13" xr3:uid="{CA0D0D81-2959-4048-B568-C2A3ECAE3564}" uniqueName="13" name="Salidas Total" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{7662A870-E3B2-4154-B61C-1FBF71041EC3}" uniqueName="14" name="OcupTotal" queryTableFieldId="14"/>
     <tableColumn id="15" xr3:uid="{D9DFDC86-A607-4E1A-AC03-BA515BCBAFFD}" uniqueName="15" name="Rechazados acumulados" queryTableFieldId="15"/>
-    <tableColumn id="17" xr3:uid="{C1FC1DA5-EF45-4471-8849-5F495E3FF680}" uniqueName="17" name="% Utilización Total" queryTableFieldId="17" dataDxfId="103">
+    <tableColumn id="17" xr3:uid="{C1FC1DA5-EF45-4471-8849-5F495E3FF680}" uniqueName="17" name="% Utilización Total" queryTableFieldId="17" dataDxfId="45">
       <calculatedColumnFormula>+output[[#This Row],[OcupTotal]]/264</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{5E209660-3C78-463E-8A28-FB880F017BEF}" uniqueName="18" name="% Utilización Externo" queryTableFieldId="18" dataDxfId="102">
+    <tableColumn id="18" xr3:uid="{5E209660-3C78-463E-8A28-FB880F017BEF}" uniqueName="18" name="% Utilización Externo" queryTableFieldId="18" dataDxfId="44">
       <calculatedColumnFormula>+output[[#This Row],[Ocupación Externo]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A5807F5A-8F30-44BB-AB84-52E671F2A0A3}" uniqueName="19" name="% Utilización Central" queryTableFieldId="19" dataDxfId="101">
+    <tableColumn id="19" xr3:uid="{A5807F5A-8F30-44BB-AB84-52E671F2A0A3}" uniqueName="19" name="% Utilización Central" queryTableFieldId="19" dataDxfId="43">
       <calculatedColumnFormula>+output[[#This Row],[Ocupación Central]]/73</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{E58CA651-F54D-4F7B-A992-F3575454629B}" uniqueName="20" name="% Utilización Polideportivo" queryTableFieldId="20" dataDxfId="100">
+    <tableColumn id="20" xr3:uid="{E58CA651-F54D-4F7B-A992-F3575454629B}" uniqueName="20" name="% Utilización Polideportivo" queryTableFieldId="20" dataDxfId="42">
       <calculatedColumnFormula>+output[[#This Row],[Ocupación Polideportivo]]/91</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{CBA7D8CD-20EB-41E6-B1A4-A2DEF8230906}" uniqueName="21" name="Rechazados por hora" queryTableFieldId="21" dataDxfId="27">
+    <tableColumn id="21" xr3:uid="{CBA7D8CD-20EB-41E6-B1A4-A2DEF8230906}" uniqueName="21" name="Rechazados por hora" queryTableFieldId="21" dataDxfId="41">
       <calculatedColumnFormula>+output[[#This Row],[Rechazados acumulados]]-O1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1691,7 +1108,6 @@
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="2"/>
     <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1723,13 +1139,13 @@
       <c r="H1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>38</v>
       </c>
       <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
       <c r="L1" t="s">
@@ -1791,7 +1207,7 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2">
         <v>26</v>
       </c>
       <c r="L2">
@@ -1803,26 +1219,26 @@
       <c r="N2">
         <v>80</v>
       </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.30303030303030304</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.31</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.31506849315068491</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2">
         <v>0</v>
       </c>
     </row>
@@ -1857,7 +1273,7 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3">
         <v>46</v>
       </c>
       <c r="L3">
@@ -1872,23 +1288,23 @@
       <c r="O3">
         <v>1</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.54545454545454541</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.57534246575342463</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.50549450549450547</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T3">
         <f>+output[[#This Row],[Rechazados acumulados]]-O2</f>
         <v>1</v>
       </c>
@@ -1924,7 +1340,7 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4">
         <v>60</v>
       </c>
       <c r="L4">
@@ -1939,23 +1355,23 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.73106060606060608</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.75</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.79452054794520544</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.65934065934065933</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4">
         <f>+output[[#This Row],[Rechazados acumulados]]-O3</f>
         <v>0</v>
       </c>
@@ -1991,7 +1407,7 @@
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5">
         <v>67</v>
       </c>
       <c r="L5">
@@ -2006,23 +1422,23 @@
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.85227272727272729</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.94</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.87671232876712324</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.73626373626373631</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5">
         <f>+output[[#This Row],[Rechazados acumulados]]-O4</f>
         <v>0</v>
       </c>
@@ -2058,7 +1474,7 @@
       <c r="J6">
         <v>11</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <v>71</v>
       </c>
       <c r="L6">
@@ -2073,23 +1489,23 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.85984848484848486</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.95</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.83561643835616439</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.78021978021978022</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6">
         <f>+output[[#This Row],[Rechazados acumulados]]-O5</f>
         <v>0</v>
       </c>
@@ -2125,7 +1541,7 @@
       <c r="J7">
         <v>16</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7">
         <v>64</v>
       </c>
       <c r="L7">
@@ -2140,23 +1556,23 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.76515151515151514</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.85</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.72602739726027399</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.70329670329670335</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7">
         <f>+output[[#This Row],[Rechazados acumulados]]-O6</f>
         <v>0</v>
       </c>
@@ -2192,7 +1608,7 @@
       <c r="J8">
         <v>17</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8">
         <v>59</v>
       </c>
       <c r="L8">
@@ -2207,23 +1623,23 @@
       <c r="O8">
         <v>1</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.68560606060606055</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.73</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.67123287671232879</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.64835164835164838</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8">
         <f>+output[[#This Row],[Rechazados acumulados]]-O7</f>
         <v>0</v>
       </c>
@@ -2259,7 +1675,7 @@
       <c r="J9">
         <v>12</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9">
         <v>61</v>
       </c>
       <c r="L9">
@@ -2274,23 +1690,23 @@
       <c r="O9">
         <v>1</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.64015151515151514</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.59</v>
       </c>
-      <c r="R9" s="4">
+      <c r="R9" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.67123287671232879</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.67032967032967028</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9">
         <f>+output[[#This Row],[Rechazados acumulados]]-O8</f>
         <v>0</v>
       </c>
@@ -2326,7 +1742,7 @@
       <c r="J10">
         <v>16</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10">
         <v>58</v>
       </c>
       <c r="L10">
@@ -2341,23 +1757,23 @@
       <c r="O10">
         <v>1</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.61742424242424243</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.67123287671232879</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.63736263736263732</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10">
         <f>+output[[#This Row],[Rechazados acumulados]]-O9</f>
         <v>0</v>
       </c>
@@ -2393,7 +1809,7 @@
       <c r="J11">
         <v>13</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11">
         <v>57</v>
       </c>
       <c r="L11">
@@ -2408,23 +1824,23 @@
       <c r="O11">
         <v>1</v>
       </c>
-      <c r="P11" s="4">
+      <c r="P11" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.60606060606060608</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.64383561643835618</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.62637362637362637</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11">
         <f>+output[[#This Row],[Rechazados acumulados]]-O10</f>
         <v>0</v>
       </c>
@@ -2460,7 +1876,7 @@
       <c r="J12">
         <v>10</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12">
         <v>77</v>
       </c>
       <c r="L12">
@@ -2475,23 +1891,23 @@
       <c r="O12">
         <v>2</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.81060606060606055</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.78</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.80821917808219179</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.84615384615384615</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12">
         <f>+output[[#This Row],[Rechazados acumulados]]-O11</f>
         <v>1</v>
       </c>
@@ -2527,7 +1943,7 @@
       <c r="J13">
         <v>13</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13">
         <v>91</v>
       </c>
       <c r="L13">
@@ -2542,23 +1958,23 @@
       <c r="O13">
         <v>4</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.98106060606060608</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.98</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.95890410958904104</v>
       </c>
-      <c r="S13" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T13" s="5">
+      <c r="S13" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T13">
         <f>+output[[#This Row],[Rechazados acumulados]]-O12</f>
         <v>2</v>
       </c>
@@ -2594,7 +2010,7 @@
       <c r="J14">
         <v>14</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14">
         <v>91</v>
       </c>
       <c r="L14">
@@ -2609,23 +2025,23 @@
       <c r="O14">
         <v>4</v>
       </c>
-      <c r="P14" s="4">
-        <f>+output[[#This Row],[OcupTotal]]/264</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R14" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S14" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T14" s="5">
+      <c r="P14" s="2">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S14" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T14">
         <f>+output[[#This Row],[Rechazados acumulados]]-O13</f>
         <v>0</v>
       </c>
@@ -2661,7 +2077,7 @@
       <c r="J15">
         <v>12</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15">
         <v>91</v>
       </c>
       <c r="L15">
@@ -2676,23 +2092,23 @@
       <c r="O15">
         <v>4</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.96969696969696972</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.92</v>
       </c>
-      <c r="R15" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S15" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T15" s="5">
+      <c r="R15" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T15">
         <f>+output[[#This Row],[Rechazados acumulados]]-O14</f>
         <v>0</v>
       </c>
@@ -2728,7 +2144,7 @@
       <c r="J16">
         <v>20</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16">
         <v>81</v>
       </c>
       <c r="L16">
@@ -2743,23 +2159,23 @@
       <c r="O16">
         <v>4</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.87121212121212122</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.82</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.9178082191780822</v>
       </c>
-      <c r="S16" s="3">
+      <c r="S16" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.89010989010989006</v>
       </c>
-      <c r="T16" s="5">
+      <c r="T16">
         <f>+output[[#This Row],[Rechazados acumulados]]-O15</f>
         <v>0</v>
       </c>
@@ -2822,11 +2238,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.65753424657534243</v>
       </c>
-      <c r="S17" s="5">
+      <c r="S17">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.64835164835164838</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17">
         <f>+output[[#This Row],[Rechazados acumulados]]-O16</f>
         <v>0</v>
       </c>
@@ -2889,11 +2305,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.42465753424657532</v>
       </c>
-      <c r="S18" s="5">
+      <c r="S18">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.37362637362637363</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18">
         <f>+output[[#This Row],[Rechazados acumulados]]-O17</f>
         <v>0</v>
       </c>
@@ -2956,11 +2372,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.19178082191780821</v>
       </c>
-      <c r="S19" s="5">
+      <c r="S19">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.26373626373626374</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19">
         <f>+output[[#This Row],[Rechazados acumulados]]-O18</f>
         <v>0</v>
       </c>
@@ -3023,11 +2439,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>9.5890410958904104E-2</v>
       </c>
-      <c r="S20" s="5">
+      <c r="S20">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="T20" s="5">
+      <c r="T20">
         <f>+output[[#This Row],[Rechazados acumulados]]-O19</f>
         <v>0</v>
       </c>
@@ -3090,11 +2506,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>1.3698630136986301E-2</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>6.5934065934065936E-2</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21">
         <f>+output[[#This Row],[Rechazados acumulados]]-O20</f>
         <v>0</v>
       </c>
@@ -3157,11 +2573,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0</v>
       </c>
-      <c r="S22" s="5">
+      <c r="S22">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>1.098901098901099E-2</v>
       </c>
-      <c r="T22" s="5">
+      <c r="T22">
         <f>+output[[#This Row],[Rechazados acumulados]]-O21</f>
         <v>0</v>
       </c>
@@ -3197,7 +2613,7 @@
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23">
         <v>38</v>
       </c>
       <c r="L23">
@@ -3212,23 +2628,23 @@
       <c r="O23">
         <v>10</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.32196969696969696</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.24657534246575341</v>
       </c>
-      <c r="S23" s="3">
+      <c r="S23" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.4175824175824176</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23">
         <f>+output[[#This Row],[Rechazados acumulados]]-O22</f>
         <v>6</v>
       </c>
@@ -3264,7 +2680,7 @@
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24">
         <v>55</v>
       </c>
       <c r="L24">
@@ -3279,23 +2695,23 @@
       <c r="O24">
         <v>10</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.57954545454545459</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.61</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.50684931506849318</v>
       </c>
-      <c r="S24" s="3">
+      <c r="S24" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.60439560439560436</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24">
         <f>+output[[#This Row],[Rechazados acumulados]]-O23</f>
         <v>0</v>
       </c>
@@ -3331,7 +2747,7 @@
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25">
         <v>64</v>
       </c>
       <c r="L25">
@@ -3346,23 +2762,23 @@
       <c r="O25">
         <v>10</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.71969696969696972</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="Q25" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.78</v>
       </c>
-      <c r="R25" s="3">
+      <c r="R25" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.65753424657534243</v>
       </c>
-      <c r="S25" s="3">
+      <c r="S25" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.70329670329670335</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25">
         <f>+output[[#This Row],[Rechazados acumulados]]-O24</f>
         <v>0</v>
       </c>
@@ -3398,7 +2814,7 @@
       <c r="J26">
         <v>6</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26">
         <v>69</v>
       </c>
       <c r="L26">
@@ -3413,23 +2829,23 @@
       <c r="O26">
         <v>10</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.78787878787878785</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.86</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.72602739726027399</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.75824175824175821</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26">
         <f>+output[[#This Row],[Rechazados acumulados]]-O25</f>
         <v>0</v>
       </c>
@@ -3465,7 +2881,7 @@
       <c r="J27">
         <v>14</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27">
         <v>64</v>
       </c>
       <c r="L27">
@@ -3480,23 +2896,23 @@
       <c r="O27">
         <v>10</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.78030303030303028</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.86</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.76712328767123283</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.70329670329670335</v>
       </c>
-      <c r="T27" s="5">
+      <c r="T27">
         <f>+output[[#This Row],[Rechazados acumulados]]-O26</f>
         <v>0</v>
       </c>
@@ -3532,7 +2948,7 @@
       <c r="J28">
         <v>17</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K28">
         <v>57</v>
       </c>
       <c r="L28">
@@ -3547,23 +2963,23 @@
       <c r="O28">
         <v>10</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.70454545454545459</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="Q28" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.78</v>
       </c>
-      <c r="R28" s="3">
+      <c r="R28" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.69863013698630139</v>
       </c>
-      <c r="S28" s="3">
+      <c r="S28" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.62637362637362637</v>
       </c>
-      <c r="T28" s="5">
+      <c r="T28">
         <f>+output[[#This Row],[Rechazados acumulados]]-O27</f>
         <v>0</v>
       </c>
@@ -3599,7 +3015,7 @@
       <c r="J29">
         <v>15</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29">
         <v>50</v>
       </c>
       <c r="L29">
@@ -3614,23 +3030,23 @@
       <c r="O29">
         <v>10</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.625</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.74</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.5494505494505495</v>
       </c>
-      <c r="T29" s="5">
+      <c r="T29">
         <f>+output[[#This Row],[Rechazados acumulados]]-O28</f>
         <v>0</v>
       </c>
@@ -3666,7 +3082,7 @@
       <c r="J30">
         <v>16</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30">
         <v>55</v>
       </c>
       <c r="L30">
@@ -3681,23 +3097,23 @@
       <c r="O30">
         <v>10</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.61363636363636365</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.64</v>
       </c>
-      <c r="R30" s="3">
+      <c r="R30" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.58904109589041098</v>
       </c>
-      <c r="S30" s="3">
+      <c r="S30" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.60439560439560436</v>
       </c>
-      <c r="T30" s="5">
+      <c r="T30">
         <f>+output[[#This Row],[Rechazados acumulados]]-O29</f>
         <v>0</v>
       </c>
@@ -3733,7 +3149,7 @@
       <c r="J31">
         <v>11</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31">
         <v>57</v>
       </c>
       <c r="L31">
@@ -3748,23 +3164,23 @@
       <c r="O31">
         <v>10</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P31" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="Q31" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.61</v>
       </c>
-      <c r="R31" s="3">
+      <c r="R31" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.49315068493150682</v>
       </c>
-      <c r="S31" s="3">
+      <c r="S31" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.62637362637362637</v>
       </c>
-      <c r="T31" s="5">
+      <c r="T31">
         <f>+output[[#This Row],[Rechazados acumulados]]-O30</f>
         <v>0</v>
       </c>
@@ -3800,7 +3216,7 @@
       <c r="J32">
         <v>8</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32">
         <v>65</v>
       </c>
       <c r="L32">
@@ -3815,23 +3231,23 @@
       <c r="O32">
         <v>10</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.61363636363636365</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="T32" s="5">
+      <c r="T32">
         <f>+output[[#This Row],[Rechazados acumulados]]-O31</f>
         <v>0</v>
       </c>
@@ -3867,7 +3283,7 @@
       <c r="J33">
         <v>13</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33">
         <v>88</v>
       </c>
       <c r="L33">
@@ -3882,23 +3298,23 @@
       <c r="O33">
         <v>13</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.84469696969696972</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.73</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.84931506849315064</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.96703296703296704</v>
       </c>
-      <c r="T33" s="5">
+      <c r="T33">
         <f>+output[[#This Row],[Rechazados acumulados]]-O32</f>
         <v>3</v>
       </c>
@@ -3934,7 +3350,7 @@
       <c r="J34">
         <v>12</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34">
         <v>91</v>
       </c>
       <c r="L34">
@@ -3949,23 +3365,23 @@
       <c r="O34">
         <v>16</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.99242424242424243</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.98</v>
       </c>
-      <c r="R34" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S34" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T34" s="5">
+      <c r="R34" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S34" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T34">
         <f>+output[[#This Row],[Rechazados acumulados]]-O33</f>
         <v>3</v>
       </c>
@@ -4001,7 +3417,7 @@
       <c r="J35">
         <v>8</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35">
         <v>91</v>
       </c>
       <c r="L35">
@@ -4016,23 +3432,23 @@
       <c r="O35">
         <v>16</v>
       </c>
-      <c r="P35" s="4">
-        <f>+output[[#This Row],[OcupTotal]]/264</f>
-        <v>1</v>
-      </c>
-      <c r="Q35" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R35" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S35" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T35" s="5">
+      <c r="P35" s="2">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R35" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S35" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T35">
         <f>+output[[#This Row],[Rechazados acumulados]]-O34</f>
         <v>0</v>
       </c>
@@ -4068,7 +3484,7 @@
       <c r="J36">
         <v>18</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36">
         <v>91</v>
       </c>
       <c r="L36">
@@ -4083,23 +3499,23 @@
       <c r="O36">
         <v>16</v>
       </c>
-      <c r="P36" s="4">
-        <f>+output[[#This Row],[OcupTotal]]/264</f>
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R36" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S36" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T36" s="5">
+      <c r="P36" s="2">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R36" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S36" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T36">
         <f>+output[[#This Row],[Rechazados acumulados]]-O35</f>
         <v>0</v>
       </c>
@@ -4135,7 +3551,7 @@
       <c r="J37">
         <v>32</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K37">
         <v>81</v>
       </c>
       <c r="L37">
@@ -4150,23 +3566,23 @@
       <c r="O37">
         <v>16</v>
       </c>
-      <c r="P37" s="4">
+      <c r="P37" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.94318181818181823</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q37" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.95</v>
       </c>
-      <c r="R37" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S37" s="3">
+      <c r="R37" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S37" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.89010989010989006</v>
       </c>
-      <c r="T37" s="5">
+      <c r="T37">
         <f>+output[[#This Row],[Rechazados acumulados]]-O36</f>
         <v>0</v>
       </c>
@@ -4229,11 +3645,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.75342465753424659</v>
       </c>
-      <c r="S38" s="5">
+      <c r="S38">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.72527472527472525</v>
       </c>
-      <c r="T38" s="5">
+      <c r="T38">
         <f>+output[[#This Row],[Rechazados acumulados]]-O37</f>
         <v>0</v>
       </c>
@@ -4296,11 +3712,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.46575342465753422</v>
       </c>
-      <c r="S39" s="5">
+      <c r="S39">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.50549450549450547</v>
       </c>
-      <c r="T39" s="5">
+      <c r="T39">
         <f>+output[[#This Row],[Rechazados acumulados]]-O38</f>
         <v>0</v>
       </c>
@@ -4363,11 +3779,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.36986301369863012</v>
       </c>
-      <c r="S40" s="5">
+      <c r="S40">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="T40" s="5">
+      <c r="T40">
         <f>+output[[#This Row],[Rechazados acumulados]]-O39</f>
         <v>0</v>
       </c>
@@ -4430,11 +3846,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.15068493150684931</v>
       </c>
-      <c r="S41" s="5">
+      <c r="S41">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="T41" s="5">
+      <c r="T41">
         <f>+output[[#This Row],[Rechazados acumulados]]-O40</f>
         <v>0</v>
       </c>
@@ -4497,11 +3913,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>5.4794520547945202E-2</v>
       </c>
-      <c r="S42" s="5">
+      <c r="S42">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="T42" s="5">
+      <c r="T42">
         <f>+output[[#This Row],[Rechazados acumulados]]-O41</f>
         <v>0</v>
       </c>
@@ -4564,11 +3980,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>1.3698630136986301E-2</v>
       </c>
-      <c r="S43" s="5">
+      <c r="S43">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>1.098901098901099E-2</v>
       </c>
-      <c r="T43" s="5">
+      <c r="T43">
         <f>+output[[#This Row],[Rechazados acumulados]]-O42</f>
         <v>0</v>
       </c>
@@ -4631,11 +4047,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>1.3698630136986301E-2</v>
       </c>
-      <c r="S44" s="5">
+      <c r="S44">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>1.098901098901099E-2</v>
       </c>
-      <c r="T44" s="5">
+      <c r="T44">
         <f>+output[[#This Row],[Rechazados acumulados]]-O43</f>
         <v>0</v>
       </c>
@@ -4698,11 +4114,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>1.3698630136986301E-2</v>
       </c>
-      <c r="S45" s="5">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>0</v>
-      </c>
-      <c r="T45" s="5">
+      <c r="S45">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T45">
         <f>+output[[#This Row],[Rechazados acumulados]]-O44</f>
         <v>0</v>
       </c>
@@ -4738,7 +4154,7 @@
       <c r="J46">
         <v>0</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46">
         <v>21</v>
       </c>
       <c r="L46">
@@ -4753,23 +4169,23 @@
       <c r="O46">
         <v>17</v>
       </c>
-      <c r="P46" s="4">
+      <c r="P46" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.38356164383561642</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="T46" s="5">
+      <c r="T46">
         <f>+output[[#This Row],[Rechazados acumulados]]-O45</f>
         <v>1</v>
       </c>
@@ -4805,7 +4221,7 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47">
         <v>46</v>
       </c>
       <c r="L47">
@@ -4820,23 +4236,23 @@
       <c r="O47">
         <v>17</v>
       </c>
-      <c r="P47" s="4">
+      <c r="P47" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.61363636363636365</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.65</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.69863013698630139</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.50549450549450547</v>
       </c>
-      <c r="T47" s="5">
+      <c r="T47">
         <f>+output[[#This Row],[Rechazados acumulados]]-O46</f>
         <v>0</v>
       </c>
@@ -4872,7 +4288,7 @@
       <c r="J48">
         <v>0</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48">
         <v>63</v>
       </c>
       <c r="L48">
@@ -4887,23 +4303,23 @@
       <c r="O48">
         <v>17</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P48" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.75</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.78</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.78082191780821919</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.69230769230769229</v>
       </c>
-      <c r="T48" s="5">
+      <c r="T48">
         <f>+output[[#This Row],[Rechazados acumulados]]-O47</f>
         <v>0</v>
       </c>
@@ -4939,7 +4355,7 @@
       <c r="J49">
         <v>5</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49">
         <v>73</v>
       </c>
       <c r="L49">
@@ -4954,23 +4370,23 @@
       <c r="O49">
         <v>17</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P49" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.84090909090909094</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.89</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.82191780821917804</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.80219780219780223</v>
       </c>
-      <c r="T49" s="5">
+      <c r="T49">
         <f>+output[[#This Row],[Rechazados acumulados]]-O48</f>
         <v>0</v>
       </c>
@@ -5006,7 +4422,7 @@
       <c r="J50">
         <v>9</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50">
         <v>77</v>
       </c>
       <c r="L50">
@@ -5021,23 +4437,23 @@
       <c r="O50">
         <v>17</v>
       </c>
-      <c r="P50" s="4">
+      <c r="P50" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.85227272727272729</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.94</v>
       </c>
-      <c r="R50" s="3">
+      <c r="R50" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.73972602739726023</v>
       </c>
-      <c r="S50" s="3">
+      <c r="S50" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.84615384615384615</v>
       </c>
-      <c r="T50" s="5">
+      <c r="T50">
         <f>+output[[#This Row],[Rechazados acumulados]]-O49</f>
         <v>0</v>
       </c>
@@ -5073,7 +4489,7 @@
       <c r="J51">
         <v>11</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51">
         <v>73</v>
       </c>
       <c r="L51">
@@ -5088,23 +4504,23 @@
       <c r="O51">
         <v>17</v>
       </c>
-      <c r="P51" s="4">
+      <c r="P51" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.78030303030303028</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.82</v>
       </c>
-      <c r="R51" s="3">
+      <c r="R51" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.69863013698630139</v>
       </c>
-      <c r="S51" s="3">
+      <c r="S51" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.80219780219780223</v>
       </c>
-      <c r="T51" s="5">
+      <c r="T51">
         <f>+output[[#This Row],[Rechazados acumulados]]-O50</f>
         <v>0</v>
       </c>
@@ -5140,7 +4556,7 @@
       <c r="J52">
         <v>29</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52">
         <v>50</v>
       </c>
       <c r="L52">
@@ -5155,23 +4571,23 @@
       <c r="O52">
         <v>17</v>
       </c>
-      <c r="P52" s="4">
+      <c r="P52" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.63257575757575757</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.74</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.58904109589041098</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.5494505494505495</v>
       </c>
-      <c r="T52" s="5">
+      <c r="T52">
         <f>+output[[#This Row],[Rechazados acumulados]]-O51</f>
         <v>0</v>
       </c>
@@ -5207,7 +4623,7 @@
       <c r="J53">
         <v>17</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53">
         <v>44</v>
       </c>
       <c r="L53">
@@ -5222,23 +4638,23 @@
       <c r="O53">
         <v>17</v>
       </c>
-      <c r="P53" s="4">
+      <c r="P53" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.55681818181818177</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.63</v>
       </c>
-      <c r="R53" s="3">
+      <c r="R53" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.54794520547945202</v>
       </c>
-      <c r="S53" s="3">
+      <c r="S53" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.48351648351648352</v>
       </c>
-      <c r="T53" s="5">
+      <c r="T53">
         <f>+output[[#This Row],[Rechazados acumulados]]-O52</f>
         <v>0</v>
       </c>
@@ -5274,7 +4690,7 @@
       <c r="J54">
         <v>11</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54">
         <v>50</v>
       </c>
       <c r="L54">
@@ -5289,23 +4705,23 @@
       <c r="O54">
         <v>17</v>
       </c>
-      <c r="P54" s="4">
+      <c r="P54" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.53787878787878785</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.52</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.54794520547945202</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.5494505494505495</v>
       </c>
-      <c r="T54" s="5">
+      <c r="T54">
         <f>+output[[#This Row],[Rechazados acumulados]]-O53</f>
         <v>0</v>
       </c>
@@ -5341,7 +4757,7 @@
       <c r="J55">
         <v>11</v>
       </c>
-      <c r="K55" s="2">
+      <c r="K55">
         <v>46</v>
       </c>
       <c r="L55">
@@ -5356,23 +4772,23 @@
       <c r="O55">
         <v>17</v>
       </c>
-      <c r="P55" s="4">
+      <c r="P55" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R55" s="3">
+      <c r="R55" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="S55" s="3">
+      <c r="S55" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.50549450549450547</v>
       </c>
-      <c r="T55" s="5">
+      <c r="T55">
         <f>+output[[#This Row],[Rechazados acumulados]]-O54</f>
         <v>0</v>
       </c>
@@ -5408,7 +4824,7 @@
       <c r="J56">
         <v>6</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56">
         <v>69</v>
       </c>
       <c r="L56">
@@ -5423,23 +4839,23 @@
       <c r="O56">
         <v>19</v>
       </c>
-      <c r="P56" s="4">
+      <c r="P56" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.76893939393939392</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.74</v>
       </c>
-      <c r="R56" s="3">
+      <c r="R56" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.82191780821917804</v>
       </c>
-      <c r="S56" s="3">
+      <c r="S56" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.75824175824175821</v>
       </c>
-      <c r="T56" s="5">
+      <c r="T56">
         <f>+output[[#This Row],[Rechazados acumulados]]-O55</f>
         <v>2</v>
       </c>
@@ -5475,7 +4891,7 @@
       <c r="J57">
         <v>10</v>
       </c>
-      <c r="K57" s="2">
+      <c r="K57">
         <v>91</v>
       </c>
       <c r="L57">
@@ -5490,23 +4906,23 @@
       <c r="O57">
         <v>22</v>
       </c>
-      <c r="P57" s="4">
+      <c r="P57" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.99621212121212122</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.99</v>
       </c>
-      <c r="R57" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S57" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T57" s="5">
+      <c r="R57" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S57" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T57">
         <f>+output[[#This Row],[Rechazados acumulados]]-O56</f>
         <v>3</v>
       </c>
@@ -5542,7 +4958,7 @@
       <c r="J58">
         <v>9</v>
       </c>
-      <c r="K58" s="2">
+      <c r="K58">
         <v>91</v>
       </c>
       <c r="L58">
@@ -5557,23 +4973,23 @@
       <c r="O58">
         <v>22</v>
       </c>
-      <c r="P58" s="4">
-        <f>+output[[#This Row],[OcupTotal]]/264</f>
-        <v>1</v>
-      </c>
-      <c r="Q58" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R58" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S58" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T58" s="5">
+      <c r="P58" s="2">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q58" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R58" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S58" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T58">
         <f>+output[[#This Row],[Rechazados acumulados]]-O57</f>
         <v>0</v>
       </c>
@@ -5609,7 +5025,7 @@
       <c r="J59">
         <v>13</v>
       </c>
-      <c r="K59" s="2">
+      <c r="K59">
         <v>91</v>
       </c>
       <c r="L59">
@@ -5624,23 +5040,23 @@
       <c r="O59">
         <v>22</v>
       </c>
-      <c r="P59" s="4">
-        <f>+output[[#This Row],[OcupTotal]]/264</f>
-        <v>1</v>
-      </c>
-      <c r="Q59" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R59" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S59" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T59" s="5">
+      <c r="P59" s="2">
+        <f>+output[[#This Row],[OcupTotal]]/264</f>
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R59" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S59" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T59">
         <f>+output[[#This Row],[Rechazados acumulados]]-O58</f>
         <v>0</v>
       </c>
@@ -5676,7 +5092,7 @@
       <c r="J60">
         <v>22</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K60">
         <v>79</v>
       </c>
       <c r="L60">
@@ -5691,23 +5107,23 @@
       <c r="O60">
         <v>22</v>
       </c>
-      <c r="P60" s="4">
+      <c r="P60" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.95454545454545459</v>
       </c>
-      <c r="Q60" s="3">
-        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
-        <v>1</v>
-      </c>
-      <c r="R60" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="Q60" s="2">
+        <f>+output[[#This Row],[Ocupación Externo]]/100</f>
+        <v>1</v>
+      </c>
+      <c r="R60" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S60" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.86813186813186816</v>
       </c>
-      <c r="T60" s="5">
+      <c r="T60">
         <f>+output[[#This Row],[Rechazados acumulados]]-O59</f>
         <v>0</v>
       </c>
@@ -5770,11 +5186,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.86301369863013699</v>
       </c>
-      <c r="S61" s="5">
+      <c r="S61">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.60439560439560436</v>
       </c>
-      <c r="T61" s="5">
+      <c r="T61">
         <f>+output[[#This Row],[Rechazados acumulados]]-O60</f>
         <v>0</v>
       </c>
@@ -5837,11 +5253,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.58904109589041098</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.46153846153846156</v>
       </c>
-      <c r="T62" s="5">
+      <c r="T62">
         <f>+output[[#This Row],[Rechazados acumulados]]-O61</f>
         <v>0</v>
       </c>
@@ -5904,11 +5320,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.41095890410958902</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.2967032967032967</v>
       </c>
-      <c r="T63" s="5">
+      <c r="T63">
         <f>+output[[#This Row],[Rechazados acumulados]]-O62</f>
         <v>0</v>
       </c>
@@ -5971,11 +5387,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.24657534246575341</v>
       </c>
-      <c r="S64" s="5">
+      <c r="S64">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>8.7912087912087919E-2</v>
       </c>
-      <c r="T64" s="5">
+      <c r="T64">
         <f>+output[[#This Row],[Rechazados acumulados]]-O63</f>
         <v>0</v>
       </c>
@@ -6038,11 +5454,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>6.8493150684931503E-2</v>
       </c>
-      <c r="S65" s="5">
+      <c r="S65">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>3.2967032967032968E-2</v>
       </c>
-      <c r="T65" s="5">
+      <c r="T65">
         <f>+output[[#This Row],[Rechazados acumulados]]-O64</f>
         <v>0</v>
       </c>
@@ -6105,11 +5521,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>2.7397260273972601E-2</v>
       </c>
-      <c r="S66" s="5">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>0</v>
-      </c>
-      <c r="T66" s="5">
+      <c r="S66">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T66">
         <f>+output[[#This Row],[Rechazados acumulados]]-O65</f>
         <v>0</v>
       </c>
@@ -6172,11 +5588,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0</v>
       </c>
-      <c r="S67" s="5">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>0</v>
-      </c>
-      <c r="T67" s="5">
+      <c r="S67">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T67">
         <f>+output[[#This Row],[Rechazados acumulados]]-O66</f>
         <v>0</v>
       </c>
@@ -6212,7 +5628,7 @@
       <c r="J68">
         <v>0</v>
       </c>
-      <c r="K68" s="2">
+      <c r="K68">
         <v>24</v>
       </c>
       <c r="L68">
@@ -6227,23 +5643,23 @@
       <c r="O68">
         <v>24</v>
       </c>
-      <c r="P68" s="4">
+      <c r="P68" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.32575757575757575</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="Q68" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.39</v>
       </c>
-      <c r="R68" s="3">
+      <c r="R68" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.31506849315068491</v>
       </c>
-      <c r="S68" s="3">
+      <c r="S68" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.26373626373626374</v>
       </c>
-      <c r="T68" s="5">
+      <c r="T68">
         <f>+output[[#This Row],[Rechazados acumulados]]-O67</f>
         <v>2</v>
       </c>
@@ -6279,7 +5695,7 @@
       <c r="J69">
         <v>0</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69">
         <v>45</v>
       </c>
       <c r="L69">
@@ -6294,23 +5710,23 @@
       <c r="O69">
         <v>25</v>
       </c>
-      <c r="P69" s="4">
+      <c r="P69" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="Q69" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.6</v>
       </c>
-      <c r="R69" s="3">
+      <c r="R69" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.52054794520547942</v>
       </c>
-      <c r="S69" s="3">
+      <c r="S69" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.49450549450549453</v>
       </c>
-      <c r="T69" s="5">
+      <c r="T69">
         <f>+output[[#This Row],[Rechazados acumulados]]-O68</f>
         <v>1</v>
       </c>
@@ -6346,7 +5762,7 @@
       <c r="J70">
         <v>0</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70">
         <v>63</v>
       </c>
       <c r="L70">
@@ -6361,23 +5777,23 @@
       <c r="O70">
         <v>26</v>
       </c>
-      <c r="P70" s="4">
+      <c r="P70" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.69318181818181823</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q70" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.76</v>
       </c>
-      <c r="R70" s="3">
+      <c r="R70" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.60273972602739723</v>
       </c>
-      <c r="S70" s="3">
+      <c r="S70" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.69230769230769229</v>
       </c>
-      <c r="T70" s="5">
+      <c r="T70">
         <f>+output[[#This Row],[Rechazados acumulados]]-O69</f>
         <v>1</v>
       </c>
@@ -6413,7 +5829,7 @@
       <c r="J71">
         <v>8</v>
       </c>
-      <c r="K71" s="2">
+      <c r="K71">
         <v>72</v>
       </c>
       <c r="L71">
@@ -6428,23 +5844,23 @@
       <c r="O71">
         <v>26</v>
       </c>
-      <c r="P71" s="4">
+      <c r="P71" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.78787878787878785</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="Q71" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.83</v>
       </c>
-      <c r="R71" s="3">
+      <c r="R71" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.72602739726027399</v>
       </c>
-      <c r="S71" s="3">
+      <c r="S71" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.79120879120879117</v>
       </c>
-      <c r="T71" s="5">
+      <c r="T71">
         <f>+output[[#This Row],[Rechazados acumulados]]-O70</f>
         <v>0</v>
       </c>
@@ -6480,7 +5896,7 @@
       <c r="J72">
         <v>8</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72">
         <v>76</v>
       </c>
       <c r="L72">
@@ -6495,23 +5911,23 @@
       <c r="O72">
         <v>28</v>
       </c>
-      <c r="P72" s="4">
+      <c r="P72" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.80681818181818177</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.81</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.76712328767123283</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.8351648351648352</v>
       </c>
-      <c r="T72" s="5">
+      <c r="T72">
         <f>+output[[#This Row],[Rechazados acumulados]]-O71</f>
         <v>2</v>
       </c>
@@ -6547,7 +5963,7 @@
       <c r="J73">
         <v>18</v>
       </c>
-      <c r="K73" s="2">
+      <c r="K73">
         <v>63</v>
       </c>
       <c r="L73">
@@ -6562,23 +5978,23 @@
       <c r="O73">
         <v>28</v>
       </c>
-      <c r="P73" s="4">
+      <c r="P73" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.70833333333333337</v>
       </c>
-      <c r="Q73" s="3">
+      <c r="Q73" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.7</v>
       </c>
-      <c r="R73" s="3">
+      <c r="R73" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.73972602739726023</v>
       </c>
-      <c r="S73" s="3">
+      <c r="S73" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.69230769230769229</v>
       </c>
-      <c r="T73" s="5">
+      <c r="T73">
         <f>+output[[#This Row],[Rechazados acumulados]]-O72</f>
         <v>0</v>
       </c>
@@ -6614,7 +6030,7 @@
       <c r="J74">
         <v>15</v>
       </c>
-      <c r="K74" s="2">
+      <c r="K74">
         <v>59</v>
       </c>
       <c r="L74">
@@ -6629,23 +6045,23 @@
       <c r="O74">
         <v>28</v>
       </c>
-      <c r="P74" s="4">
+      <c r="P74" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.625</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="Q74" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.64</v>
       </c>
-      <c r="R74" s="3">
+      <c r="R74" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.57534246575342463</v>
       </c>
-      <c r="S74" s="3">
+      <c r="S74" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.64835164835164838</v>
       </c>
-      <c r="T74" s="5">
+      <c r="T74">
         <f>+output[[#This Row],[Rechazados acumulados]]-O73</f>
         <v>0</v>
       </c>
@@ -6681,7 +6097,7 @@
       <c r="J75">
         <v>17</v>
       </c>
-      <c r="K75" s="2">
+      <c r="K75">
         <v>56</v>
       </c>
       <c r="L75">
@@ -6696,23 +6112,23 @@
       <c r="O75">
         <v>28</v>
       </c>
-      <c r="P75" s="4">
+      <c r="P75" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.61363636363636365</v>
       </c>
-      <c r="Q75" s="3">
+      <c r="Q75" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.59</v>
       </c>
-      <c r="R75" s="3">
+      <c r="R75" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.64383561643835618</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S75" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.61538461538461542</v>
       </c>
-      <c r="T75" s="5">
+      <c r="T75">
         <f>+output[[#This Row],[Rechazados acumulados]]-O74</f>
         <v>0</v>
       </c>
@@ -6748,7 +6164,7 @@
       <c r="J76">
         <v>11</v>
       </c>
-      <c r="K76" s="2">
+      <c r="K76">
         <v>61</v>
       </c>
       <c r="L76">
@@ -6763,23 +6179,23 @@
       <c r="O76">
         <v>28</v>
       </c>
-      <c r="P76" s="4">
+      <c r="P76" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.59469696969696972</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.54</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.57534246575342463</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.67032967032967028</v>
       </c>
-      <c r="T76" s="5">
+      <c r="T76">
         <f>+output[[#This Row],[Rechazados acumulados]]-O75</f>
         <v>0</v>
       </c>
@@ -6815,7 +6231,7 @@
       <c r="J77">
         <v>14</v>
       </c>
-      <c r="K77" s="2">
+      <c r="K77">
         <v>70</v>
       </c>
       <c r="L77">
@@ -6830,23 +6246,23 @@
       <c r="O77">
         <v>31</v>
       </c>
-      <c r="P77" s="4">
+      <c r="P77" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.68181818181818177</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="Q77" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="R77" s="3">
+      <c r="R77" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.75342465753424659</v>
       </c>
-      <c r="S77" s="3">
+      <c r="S77" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.76923076923076927</v>
       </c>
-      <c r="T77" s="5">
+      <c r="T77">
         <f>+output[[#This Row],[Rechazados acumulados]]-O76</f>
         <v>3</v>
       </c>
@@ -6882,7 +6298,7 @@
       <c r="J78">
         <v>10</v>
       </c>
-      <c r="K78" s="2">
+      <c r="K78">
         <v>85</v>
       </c>
       <c r="L78">
@@ -6897,23 +6313,23 @@
       <c r="O78">
         <v>32</v>
       </c>
-      <c r="P78" s="4">
+      <c r="P78" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.84848484848484851</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="Q78" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.74</v>
       </c>
-      <c r="R78" s="3">
+      <c r="R78" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.8904109589041096</v>
       </c>
-      <c r="S78" s="3">
+      <c r="S78" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.93406593406593408</v>
       </c>
-      <c r="T78" s="5">
+      <c r="T78">
         <f>+output[[#This Row],[Rechazados acumulados]]-O77</f>
         <v>1</v>
       </c>
@@ -6949,7 +6365,7 @@
       <c r="J79">
         <v>8</v>
       </c>
-      <c r="K79" s="2">
+      <c r="K79">
         <v>91</v>
       </c>
       <c r="L79">
@@ -6964,23 +6380,23 @@
       <c r="O79">
         <v>33</v>
       </c>
-      <c r="P79" s="4">
+      <c r="P79" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.9507575757575758</v>
       </c>
-      <c r="Q79" s="3">
+      <c r="Q79" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.87</v>
       </c>
-      <c r="R79" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S79" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T79" s="5">
+      <c r="R79" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S79" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T79">
         <f>+output[[#This Row],[Rechazados acumulados]]-O78</f>
         <v>1</v>
       </c>
@@ -7016,7 +6432,7 @@
       <c r="J80">
         <v>18</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80">
         <v>91</v>
       </c>
       <c r="L80">
@@ -7031,23 +6447,23 @@
       <c r="O80">
         <v>34</v>
       </c>
-      <c r="P80" s="4">
+      <c r="P80" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.97348484848484851</v>
       </c>
-      <c r="Q80" s="3">
+      <c r="Q80" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.93</v>
       </c>
-      <c r="R80" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S80" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T80" s="5">
+      <c r="R80" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S80" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T80">
         <f>+output[[#This Row],[Rechazados acumulados]]-O79</f>
         <v>1</v>
       </c>
@@ -7083,7 +6499,7 @@
       <c r="J81">
         <v>13</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81">
         <v>91</v>
       </c>
       <c r="L81">
@@ -7098,23 +6514,23 @@
       <c r="O81">
         <v>34</v>
       </c>
-      <c r="P81" s="4">
+      <c r="P81" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.96590909090909094</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.91</v>
       </c>
-      <c r="R81" s="3">
-        <f>+output[[#This Row],[Ocupación Central]]/73</f>
-        <v>1</v>
-      </c>
-      <c r="S81" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T81" s="5">
+      <c r="R81" s="2">
+        <f>+output[[#This Row],[Ocupación Central]]/73</f>
+        <v>1</v>
+      </c>
+      <c r="S81" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T81">
         <f>+output[[#This Row],[Rechazados acumulados]]-O80</f>
         <v>0</v>
       </c>
@@ -7150,7 +6566,7 @@
       <c r="J82">
         <v>23</v>
       </c>
-      <c r="K82" s="2">
+      <c r="K82">
         <v>74</v>
       </c>
       <c r="L82">
@@ -7165,23 +6581,23 @@
       <c r="O82">
         <v>34</v>
       </c>
-      <c r="P82" s="4">
+      <c r="P82" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.73863636363636365</v>
       </c>
-      <c r="Q82" s="3">
+      <c r="Q82" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.73</v>
       </c>
-      <c r="R82" s="3">
+      <c r="R82" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.65753424657534243</v>
       </c>
-      <c r="S82" s="3">
+      <c r="S82" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.81318681318681318</v>
       </c>
-      <c r="T82" s="5">
+      <c r="T82">
         <f>+output[[#This Row],[Rechazados acumulados]]-O81</f>
         <v>0</v>
       </c>
@@ -7244,11 +6660,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.49315068493150682</v>
       </c>
-      <c r="S83" s="5">
+      <c r="S83">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.59340659340659341</v>
       </c>
-      <c r="T83" s="5">
+      <c r="T83">
         <f>+output[[#This Row],[Rechazados acumulados]]-O82</f>
         <v>0</v>
       </c>
@@ -7311,11 +6727,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.38356164383561642</v>
       </c>
-      <c r="S84" s="5">
+      <c r="S84">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.37362637362637363</v>
       </c>
-      <c r="T84" s="5">
+      <c r="T84">
         <f>+output[[#This Row],[Rechazados acumulados]]-O83</f>
         <v>0</v>
       </c>
@@ -7378,11 +6794,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.20547945205479451</v>
       </c>
-      <c r="S85" s="5">
+      <c r="S85">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.18681318681318682</v>
       </c>
-      <c r="T85" s="5">
+      <c r="T85">
         <f>+output[[#This Row],[Rechazados acumulados]]-O84</f>
         <v>0</v>
       </c>
@@ -7445,11 +6861,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>2.7397260273972601E-2</v>
       </c>
-      <c r="S86" s="5">
+      <c r="S86">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>9.8901098901098897E-2</v>
       </c>
-      <c r="T86" s="5">
+      <c r="T86">
         <f>+output[[#This Row],[Rechazados acumulados]]-O85</f>
         <v>0</v>
       </c>
@@ -7512,11 +6928,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>1.3698630136986301E-2</v>
       </c>
-      <c r="S87" s="5">
+      <c r="S87">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>3.2967032967032968E-2</v>
       </c>
-      <c r="T87" s="5">
+      <c r="T87">
         <f>+output[[#This Row],[Rechazados acumulados]]-O86</f>
         <v>0</v>
       </c>
@@ -7579,11 +6995,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0</v>
       </c>
-      <c r="S88" s="5">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>0</v>
-      </c>
-      <c r="T88" s="5">
+      <c r="S88">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T88">
         <f>+output[[#This Row],[Rechazados acumulados]]-O87</f>
         <v>0</v>
       </c>
@@ -7646,11 +7062,11 @@
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0</v>
       </c>
-      <c r="S89" s="5">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>0</v>
-      </c>
-      <c r="T89" s="5">
+      <c r="S89">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>0</v>
+      </c>
+      <c r="T89">
         <f>+output[[#This Row],[Rechazados acumulados]]-O88</f>
         <v>0</v>
       </c>
@@ -7686,7 +7102,7 @@
       <c r="J90">
         <v>0</v>
       </c>
-      <c r="K90" s="2">
+      <c r="K90">
         <v>35</v>
       </c>
       <c r="L90">
@@ -7701,23 +7117,23 @@
       <c r="O90">
         <v>36</v>
       </c>
-      <c r="P90" s="4">
+      <c r="P90" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.32196969696969696</v>
       </c>
-      <c r="Q90" s="3">
+      <c r="Q90" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="R90" s="3">
+      <c r="R90" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.30136986301369861</v>
       </c>
-      <c r="S90" s="3">
+      <c r="S90" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.38461538461538464</v>
       </c>
-      <c r="T90" s="5">
+      <c r="T90">
         <f>+output[[#This Row],[Rechazados acumulados]]-O89</f>
         <v>2</v>
       </c>
@@ -7753,7 +7169,7 @@
       <c r="J91">
         <v>0</v>
       </c>
-      <c r="K91" s="2">
+      <c r="K91">
         <v>61</v>
       </c>
       <c r="L91">
@@ -7768,23 +7184,23 @@
       <c r="O91">
         <v>36</v>
       </c>
-      <c r="P91" s="4">
+      <c r="P91" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.54545454545454541</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.49</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.46575342465753422</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.67032967032967028</v>
       </c>
-      <c r="T91" s="5">
+      <c r="T91">
         <f>+output[[#This Row],[Rechazados acumulados]]-O90</f>
         <v>0</v>
       </c>
@@ -7820,7 +7236,7 @@
       <c r="J92">
         <v>1</v>
       </c>
-      <c r="K92" s="2">
+      <c r="K92">
         <v>71</v>
       </c>
       <c r="L92">
@@ -7835,23 +7251,23 @@
       <c r="O92">
         <v>36</v>
       </c>
-      <c r="P92" s="4">
+      <c r="P92" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.64772727272727271</v>
       </c>
-      <c r="Q92" s="3">
+      <c r="Q92" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.6</v>
       </c>
-      <c r="R92" s="3">
+      <c r="R92" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.54794520547945202</v>
       </c>
-      <c r="S92" s="3">
+      <c r="S92" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.78021978021978022</v>
       </c>
-      <c r="T92" s="5">
+      <c r="T92">
         <f>+output[[#This Row],[Rechazados acumulados]]-O91</f>
         <v>0</v>
       </c>
@@ -7887,7 +7303,7 @@
       <c r="J93">
         <v>1</v>
       </c>
-      <c r="K93" s="2">
+      <c r="K93">
         <v>81</v>
       </c>
       <c r="L93">
@@ -7902,23 +7318,23 @@
       <c r="O93">
         <v>37</v>
       </c>
-      <c r="P93" s="4">
+      <c r="P93" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.76893939393939392</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="Q93" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.7</v>
       </c>
-      <c r="R93" s="3">
+      <c r="R93" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.71232876712328763</v>
       </c>
-      <c r="S93" s="3">
+      <c r="S93" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.89010989010989006</v>
       </c>
-      <c r="T93" s="5">
+      <c r="T93">
         <f>+output[[#This Row],[Rechazados acumulados]]-O92</f>
         <v>1</v>
       </c>
@@ -7954,7 +7370,7 @@
       <c r="J94">
         <v>12</v>
       </c>
-      <c r="K94" s="2">
+      <c r="K94">
         <v>82</v>
       </c>
       <c r="L94">
@@ -7969,23 +7385,23 @@
       <c r="O94">
         <v>37</v>
       </c>
-      <c r="P94" s="4">
+      <c r="P94" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.78409090909090906</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.72</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.72602739726027399</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.90109890109890112</v>
       </c>
-      <c r="T94" s="5">
+      <c r="T94">
         <f>+output[[#This Row],[Rechazados acumulados]]-O93</f>
         <v>0</v>
       </c>
@@ -8021,7 +7437,7 @@
       <c r="J95">
         <v>20</v>
       </c>
-      <c r="K95" s="2">
+      <c r="K95">
         <v>75</v>
       </c>
       <c r="L95">
@@ -8036,23 +7452,23 @@
       <c r="O95">
         <v>37</v>
       </c>
-      <c r="P95" s="4">
+      <c r="P95" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.66287878787878785</v>
       </c>
-      <c r="Q95" s="3">
+      <c r="Q95" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="R95" s="3">
+      <c r="R95" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.60273972602739723</v>
       </c>
-      <c r="S95" s="3">
+      <c r="S95" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.82417582417582413</v>
       </c>
-      <c r="T95" s="5">
+      <c r="T95">
         <f>+output[[#This Row],[Rechazados acumulados]]-O94</f>
         <v>0</v>
       </c>
@@ -8088,7 +7504,7 @@
       <c r="J96">
         <v>19</v>
       </c>
-      <c r="K96" s="2">
+      <c r="K96">
         <v>62</v>
       </c>
       <c r="L96">
@@ -8103,23 +7519,23 @@
       <c r="O96">
         <v>37</v>
       </c>
-      <c r="P96" s="4">
+      <c r="P96" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.57196969696969702</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.49</v>
       </c>
-      <c r="R96" s="3">
+      <c r="R96" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.54794520547945202</v>
       </c>
-      <c r="S96" s="3">
+      <c r="S96" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.68131868131868134</v>
       </c>
-      <c r="T96" s="5">
+      <c r="T96">
         <f>+output[[#This Row],[Rechazados acumulados]]-O95</f>
         <v>0</v>
       </c>
@@ -8155,7 +7571,7 @@
       <c r="J97">
         <v>16</v>
       </c>
-      <c r="K97" s="2">
+      <c r="K97">
         <v>65</v>
       </c>
       <c r="L97">
@@ -8170,23 +7586,23 @@
       <c r="O97">
         <v>37</v>
       </c>
-      <c r="P97" s="4">
+      <c r="P97" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.54166666666666663</v>
       </c>
-      <c r="Q97" s="3">
+      <c r="Q97" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.41</v>
       </c>
-      <c r="R97" s="3">
+      <c r="R97" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.50684931506849318</v>
       </c>
-      <c r="S97" s="3">
+      <c r="S97" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="T97" s="5">
+      <c r="T97">
         <f>+output[[#This Row],[Rechazados acumulados]]-O96</f>
         <v>0</v>
       </c>
@@ -8222,7 +7638,7 @@
       <c r="J98">
         <v>13</v>
       </c>
-      <c r="K98" s="2">
+      <c r="K98">
         <v>65</v>
       </c>
       <c r="L98">
@@ -8237,23 +7653,23 @@
       <c r="O98">
         <v>37</v>
       </c>
-      <c r="P98" s="4">
+      <c r="P98" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.49242424242424243</v>
       </c>
-      <c r="Q98" s="3">
+      <c r="Q98" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.36</v>
       </c>
-      <c r="R98" s="3">
+      <c r="R98" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.39726027397260272</v>
       </c>
-      <c r="S98" s="3">
+      <c r="S98" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="T98" s="5">
+      <c r="T98">
         <f>+output[[#This Row],[Rechazados acumulados]]-O97</f>
         <v>0</v>
       </c>
@@ -8289,7 +7705,7 @@
       <c r="J99">
         <v>14</v>
       </c>
-      <c r="K99" s="2">
+      <c r="K99">
         <v>72</v>
       </c>
       <c r="L99">
@@ -8304,23 +7720,23 @@
       <c r="O99">
         <v>37</v>
       </c>
-      <c r="P99" s="4">
+      <c r="P99" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.53787878787878785</v>
       </c>
-      <c r="Q99" s="3">
+      <c r="Q99" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.37</v>
       </c>
-      <c r="R99" s="3">
+      <c r="R99" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.45205479452054792</v>
       </c>
-      <c r="S99" s="3">
+      <c r="S99" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.79120879120879117</v>
       </c>
-      <c r="T99" s="5">
+      <c r="T99">
         <f>+output[[#This Row],[Rechazados acumulados]]-O98</f>
         <v>0</v>
       </c>
@@ -8356,7 +7772,7 @@
       <c r="J100">
         <v>17</v>
       </c>
-      <c r="K100" s="2">
+      <c r="K100">
         <v>86</v>
       </c>
       <c r="L100">
@@ -8371,23 +7787,23 @@
       <c r="O100">
         <v>44</v>
       </c>
-      <c r="P100" s="4">
+      <c r="P100" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.76893939393939392</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.66</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.69863013698630139</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="2">
         <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
         <v>0.94505494505494503</v>
       </c>
-      <c r="T100" s="5">
+      <c r="T100">
         <f>+output[[#This Row],[Rechazados acumulados]]-O99</f>
         <v>7</v>
       </c>
@@ -8423,7 +7839,7 @@
       <c r="J101">
         <v>12</v>
       </c>
-      <c r="K101" s="2">
+      <c r="K101">
         <v>91</v>
       </c>
       <c r="L101">
@@ -8438,23 +7854,23 @@
       <c r="O101">
         <v>47</v>
       </c>
-      <c r="P101" s="4">
+      <c r="P101" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.91287878787878785</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.89</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.83561643835616439</v>
       </c>
-      <c r="S101" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T101" s="5">
+      <c r="S101" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T101">
         <f>+output[[#This Row],[Rechazados acumulados]]-O100</f>
         <v>3</v>
       </c>
@@ -8490,7 +7906,7 @@
       <c r="J102">
         <v>17</v>
       </c>
-      <c r="K102" s="2">
+      <c r="K102">
         <v>91</v>
       </c>
       <c r="L102">
@@ -8505,23 +7921,23 @@
       <c r="O102">
         <v>47</v>
       </c>
-      <c r="P102" s="4">
+      <c r="P102" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.93181818181818177</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.93</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.84931506849315064</v>
       </c>
-      <c r="S102" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T102" s="5">
+      <c r="S102" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T102">
         <f>+output[[#This Row],[Rechazados acumulados]]-O101</f>
         <v>0</v>
       </c>
@@ -8557,7 +7973,7 @@
       <c r="J103">
         <v>12</v>
       </c>
-      <c r="K103" s="2">
+      <c r="K103">
         <v>91</v>
       </c>
       <c r="L103">
@@ -8572,23 +7988,23 @@
       <c r="O103">
         <v>47</v>
       </c>
-      <c r="P103" s="4">
+      <c r="P103" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.93560606060606055</v>
       </c>
-      <c r="Q103" s="3">
+      <c r="Q103" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.96</v>
       </c>
-      <c r="R103" s="3">
+      <c r="R103" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.82191780821917804</v>
       </c>
-      <c r="S103" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T103" s="5">
+      <c r="S103" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T103">
         <f>+output[[#This Row],[Rechazados acumulados]]-O102</f>
         <v>0</v>
       </c>
@@ -8624,7 +8040,7 @@
       <c r="J104">
         <v>7</v>
       </c>
-      <c r="K104" s="2">
+      <c r="K104">
         <v>91</v>
       </c>
       <c r="L104">
@@ -8639,99 +8055,77 @@
       <c r="O104">
         <v>47</v>
       </c>
-      <c r="P104" s="4">
+      <c r="P104" s="2">
         <f>+output[[#This Row],[OcupTotal]]/264</f>
         <v>0.90530303030303028</v>
       </c>
-      <c r="Q104" s="3">
+      <c r="Q104" s="2">
         <f>+output[[#This Row],[Ocupación Externo]]/100</f>
         <v>0.9</v>
       </c>
-      <c r="R104" s="3">
+      <c r="R104" s="2">
         <f>+output[[#This Row],[Ocupación Central]]/73</f>
         <v>0.79452054794520544</v>
       </c>
-      <c r="S104" s="3">
-        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
-        <v>1</v>
-      </c>
-      <c r="T104" s="5">
+      <c r="S104" s="2">
+        <f>+output[[#This Row],[Ocupación Polideportivo]]/91</f>
+        <v>1</v>
+      </c>
+      <c r="T104">
         <f>+output[[#This Row],[Rechazados acumulados]]-O103</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N104">
-    <cfRule type="cellIs" dxfId="26" priority="14" operator="equal">
-      <formula>264</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
       <formula>73</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="cellIs" dxfId="23" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
       <formula>91</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P1048576">
-    <cfRule type="cellIs" dxfId="22" priority="10" operator="between">
+  <conditionalFormatting sqref="N2:N104">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+      <formula>264</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:Q1048576">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="between">
       <formula>0.5</formula>
       <formula>0.75</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P1048576">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="greaterThan">
+  <conditionalFormatting sqref="P2:R1048576">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
       <formula>0.75</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q1048576">
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="between">
+  <conditionalFormatting sqref="R2:R1048576">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="between">
       <formula>0.5</formula>
       <formula>0.75</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q1048576">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="greaterThan">
-      <formula>0.75</formula>
+  <conditionalFormatting sqref="T2:T104">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R1048576">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="between">
+  <conditionalFormatting sqref="S2:S1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
       <formula>0.5</formula>
       <formula>0.75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S1048576">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="between">
-      <formula>0.5</formula>
-      <formula>0.75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S104">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="between">
-      <formula>0.5</formula>
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S104">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
-      <formula>0.75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T104">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
